--- a/CF-Timesheet/CF_Timesheet_Template.xlsx
+++ b/CF-Timesheet/CF_Timesheet_Template.xlsx
@@ -45,7 +45,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="000B5560"/>
+      <color rgb="00015846"/>
       <sz val="20"/>
     </font>
     <font>
@@ -69,7 +69,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="000B5560"/>
+      <color rgb="00015846"/>
       <sz val="10"/>
     </font>
     <font>
@@ -91,7 +91,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000B5560"/>
+      <color rgb="00015846"/>
     </font>
     <font>
       <b val="1"/>
@@ -100,12 +100,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000B5560"/>
+      <color rgb="00015846"/>
       <sz val="16"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000848E"/>
+      <color rgb="0000C7B1"/>
       <sz val="12"/>
     </font>
     <font>
@@ -136,7 +136,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000B5560"/>
+        <fgColor rgb="00013D30"/>
       </patternFill>
     </fill>
     <fill>
@@ -146,7 +146,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000848E"/>
+        <fgColor rgb="00015846"/>
       </patternFill>
     </fill>
   </fills>
@@ -344,7 +344,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2286000" cy="762000"/>
+    <ext cx="1428750" cy="838200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -706,7 +706,7 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>[replace logo at B1 with official CF asset]</t>
+          <t>Official CF logo (from CF_TA Shop Fab.pbix)</t>
         </is>
       </c>
     </row>

--- a/CF-Timesheet/CF_Timesheet_Template.xlsx
+++ b/CF-Timesheet/CF_Timesheet_Template.xlsx
@@ -17,11 +17,12 @@
     <definedName name="EmpTable">Reference!$A$3:$D$203</definedName>
     <definedName name="TradeNames">Reference!$F$3:$F$203</definedName>
     <definedName name="TradeTable">Reference!$F$3:$I$203</definedName>
+    <definedName name="WONames">'Work Orders'!$A$3:$A$73</definedName>
+    <definedName name="WOTable">'Work Orders'!$A$3:$B$73</definedName>
     <definedName name="ShiftList">Reference!$K$3:$K$4</definedName>
     <definedName name="LocList">Reference!$L$3:$L$5</definedName>
     <definedName name="SwipeList">Reference!$M$3:$M$8</definedName>
     <definedName name="HoldUpList">Reference!$N$3:$N$13</definedName>
-    <definedName name="WOList">'Work Orders'!$A$3:$A$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -31,10 +32,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="0.0;[Red]-0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0;[Red]-0.0"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,25 +47,68 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00015846"/>
-      <sz val="20"/>
+      <sz val="22"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="006B7A77"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="006B7A77"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00B7791F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="006B7A77"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001F2A28"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F2A28"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00BF8F00"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001F2A28"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00808080"/>
-      <sz val="9"/>
+      <color rgb="006B7A77"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F2A28"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -73,46 +117,25 @@
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="006B7A77"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00BF8F00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00015846"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="00015846"/>
       <sz val="16"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="0000C7B1"/>
       <sz val="12"/>
     </font>
-    <font>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -126,31 +149,41 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00015846"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FFF3CB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00013D30"/>
+        <fgColor rgb="00EDF1F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
+        <fgColor rgb="0000C7B1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00015846"/>
+        <fgColor rgb="000A6E5A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6FAF9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4C7C3"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -160,105 +193,168 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00D5DEDC"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00D5DEDC"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00D5DEDC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00F1C232"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D5DEDC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D5DEDC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5DEDC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00C9D3D1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FFFFFF"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00FFFFFF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D5DEDC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D5DEDC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5DEDC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00D5DEDC"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="165" fontId="11" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="12" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFEB9C"/>
+          <fgColor rgb="00F4C7C3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -344,7 +440,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1428750" cy="838200"/>
+    <ext cx="1257300" cy="742950"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -654,28 +750,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P58"/>
+  <dimension ref="A1:P61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col hidden="1" width="3" customWidth="1" min="1" max="1"/>
+    <col hidden="1" width="2.5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="9.5" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="7.5" customWidth="1" min="8" max="8"/>
+    <col width="7.5" customWidth="1" min="9" max="9"/>
+    <col width="8.5" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col hidden="1" outlineLevel="1" width="10" customWidth="1" min="13" max="13"/>
+    <col hidden="1" outlineLevel="1" width="9.5" customWidth="1" min="14" max="14"/>
+    <col hidden="1" outlineLevel="1" width="22" customWidth="1" min="15" max="15"/>
+    <col hidden="1" outlineLevel="1" width="20" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="n"/>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
@@ -688,43 +785,50 @@
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="n"/>
       <c r="M1" s="1" t="n"/>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>Populate the YELLOW cells</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="1" t="n"/>
       <c r="B2" s="1" t="n"/>
       <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>TURNAROUND TIME ENTRY</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>Official CF logo (from CF_TA Shop Fab.pbix)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Ver. 1.0</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="1" t="n"/>
       <c r="B3" s="1" t="n"/>
       <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>CF Industries  •  Shop / Fab  •  Ver. 1.0 (draft)</t>
-        </is>
-      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>CF Industries  •  Shop / Fab</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Populate the yellow cells</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="n"/>
       <c r="N3" s="1" t="n"/>
       <c r="O3" s="1" t="n"/>
       <c r="P3" s="1" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="8" customHeight="1">
+      <c r="A4" s="1" t="n"/>
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
@@ -741,1496 +845,1807 @@
       <c r="O4" s="1" t="n"/>
       <c r="P4" s="1" t="n"/>
     </row>
-    <row r="5">
-      <c r="B5" s="1" t="n"/>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-      <c r="E5" s="1" t="n"/>
-      <c r="F5" s="1" t="n"/>
-      <c r="G5" s="1" t="n"/>
-      <c r="H5" s="1" t="n"/>
-      <c r="I5" s="1" t="n"/>
-      <c r="J5" s="1" t="n"/>
-      <c r="K5" s="1" t="n"/>
-      <c r="L5" s="1" t="n"/>
-      <c r="M5" s="1" t="n"/>
-      <c r="N5" s="1" t="n"/>
-      <c r="O5" s="1" t="n"/>
-      <c r="P5" s="1" t="n"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n"/>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>TA / Revision</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>WORK ORDER</t>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>DAILY DETAILS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="13" customHeight="1">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>SHIFT</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>TA / REVISION</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENT</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>PREPARED BY</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Shift</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n"/>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Posting Date</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="n"/>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>Enter SAP work order # and details here (free text OK — this box expands)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Client</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr"/>
+      <c r="F7" s="9" t="inlineStr"/>
+      <c r="H7" s="9" t="inlineStr"/>
+      <c r="K7" s="9" t="inlineStr"/>
+    </row>
+    <row r="8" ht="13" customHeight="1">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>POSTING DATE</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>CREW / AREA</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>SHEET #  (E.G. 1 OF 3)</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>APPROVED BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>CF Industries</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Prepared By</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="12" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="F9" s="9" t="inlineStr"/>
+      <c r="H9" s="9" t="inlineStr"/>
+      <c r="K9" s="9" t="inlineStr"/>
+    </row>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>LABOR</t>
+        </is>
+      </c>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>RECONCILIATION  (Hillary — expand ►)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Employee Name</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>CF ID</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Trade / Position</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Activity
 Type</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>Work Order</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>Work Order Description</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>Total
-Hours</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>RT
 Hrs</t>
         </is>
       </c>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>DT
 Hrs</t>
         </is>
       </c>
-      <c r="K11" s="12" t="inlineStr">
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>Total
+Hrs</t>
+        </is>
+      </c>
+      <c r="K12" s="12" t="inlineStr">
         <is>
           <t>Work Location</t>
         </is>
       </c>
-      <c r="L11" s="12" t="inlineStr">
+      <c r="L12" s="12" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="M12" s="13" t="inlineStr">
         <is>
           <t>Lenel
-Hours</t>
-        </is>
-      </c>
-      <c r="M11" s="12" t="inlineStr">
-        <is>
-          <t>Deviation</t>
-        </is>
-      </c>
-      <c r="N11" s="12" t="inlineStr">
+Hrs</t>
+        </is>
+      </c>
+      <c r="N12" s="13" t="inlineStr">
+        <is>
+          <t>Devi-
+ation</t>
+        </is>
+      </c>
+      <c r="O12" s="13" t="inlineStr">
         <is>
           <t>Swipe Deviation Reason</t>
         </is>
       </c>
-      <c r="O11" s="12" t="inlineStr">
+      <c r="P12" s="13" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
-      <c r="P11" s="12" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" t="inlineStr">
+    </row>
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="14">
-        <f>IFERROR(IF($B12="","",VLOOKUP($B12,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="14">
-        <f>IFERROR(IF($D12="","",VLOOKUP($D12,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="16" t="n"/>
-      <c r="H12" s="13" t="n"/>
-      <c r="I12" s="13" t="n"/>
-      <c r="J12" s="13" t="n"/>
-      <c r="K12" s="13" t="n"/>
-      <c r="L12" s="13" t="n"/>
-      <c r="M12" s="17">
-        <f>IF(OR($H12="",$L12=""),"",$H12-$L12)</f>
-        <v/>
-      </c>
-      <c r="N12" s="16" t="n"/>
-      <c r="O12" s="13" t="n"/>
-      <c r="P12" s="16" t="n"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" t="inlineStr">
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="15">
+        <f>IFERROR(IF($B13="","",VLOOKUP($B13,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="15">
+        <f>IFERROR(IF($D13="","",VLOOKUP($D13,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="16">
+        <f>IFERROR(IF($F13="","",VLOOKUP($F13,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="17" t="n"/>
+      <c r="I13" s="17" t="n"/>
+      <c r="J13" s="18">
+        <f>IF(AND($H13="",$I13=""),"",N($H13)+N($I13))</f>
+        <v/>
+      </c>
+      <c r="K13" s="14" t="n"/>
+      <c r="L13" s="19" t="n"/>
+      <c r="M13" s="17" t="n"/>
+      <c r="N13" s="20">
+        <f>IF(OR($J13="",$M13=""),"",$J13-$M13)</f>
+        <v/>
+      </c>
+      <c r="O13" s="19" t="n"/>
+      <c r="P13" s="14" t="n"/>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="14">
-        <f>IFERROR(IF($B13="","",VLOOKUP($B13,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="14">
-        <f>IFERROR(IF($D13="","",VLOOKUP($D13,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="16" t="n"/>
-      <c r="H13" s="13" t="n"/>
-      <c r="I13" s="13" t="n"/>
-      <c r="J13" s="13" t="n"/>
-      <c r="K13" s="13" t="n"/>
-      <c r="L13" s="13" t="n"/>
-      <c r="M13" s="17">
-        <f>IF(OR($H13="",$L13=""),"",$H13-$L13)</f>
-        <v/>
-      </c>
-      <c r="N13" s="16" t="n"/>
-      <c r="O13" s="13" t="n"/>
-      <c r="P13" s="16" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" t="inlineStr">
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="21">
+        <f>IFERROR(IF($B14="","",VLOOKUP($B14,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="21">
+        <f>IFERROR(IF($D14="","",VLOOKUP($D14,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="22">
+        <f>IFERROR(IF($F14="","",VLOOKUP($F14,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="17" t="n"/>
+      <c r="I14" s="17" t="n"/>
+      <c r="J14" s="23">
+        <f>IF(AND($H14="",$I14=""),"",N($H14)+N($I14))</f>
+        <v/>
+      </c>
+      <c r="K14" s="14" t="n"/>
+      <c r="L14" s="19" t="n"/>
+      <c r="M14" s="17" t="n"/>
+      <c r="N14" s="24">
+        <f>IF(OR($J14="",$M14=""),"",$J14-$M14)</f>
+        <v/>
+      </c>
+      <c r="O14" s="19" t="n"/>
+      <c r="P14" s="14" t="n"/>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="14">
-        <f>IFERROR(IF($B14="","",VLOOKUP($B14,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="14">
-        <f>IFERROR(IF($D14="","",VLOOKUP($D14,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="13" t="n"/>
-      <c r="I14" s="13" t="n"/>
-      <c r="J14" s="13" t="n"/>
-      <c r="K14" s="13" t="n"/>
-      <c r="L14" s="13" t="n"/>
-      <c r="M14" s="17">
-        <f>IF(OR($H14="",$L14=""),"",$H14-$L14)</f>
-        <v/>
-      </c>
-      <c r="N14" s="16" t="n"/>
-      <c r="O14" s="13" t="n"/>
-      <c r="P14" s="16" t="n"/>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" t="inlineStr">
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="15">
+        <f>IFERROR(IF($B15="","",VLOOKUP($B15,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="15">
+        <f>IFERROR(IF($D15="","",VLOOKUP($D15,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="16">
+        <f>IFERROR(IF($F15="","",VLOOKUP($F15,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="17" t="n"/>
+      <c r="I15" s="17" t="n"/>
+      <c r="J15" s="18">
+        <f>IF(AND($H15="",$I15=""),"",N($H15)+N($I15))</f>
+        <v/>
+      </c>
+      <c r="K15" s="14" t="n"/>
+      <c r="L15" s="19" t="n"/>
+      <c r="M15" s="17" t="n"/>
+      <c r="N15" s="20">
+        <f>IF(OR($J15="",$M15=""),"",$J15-$M15)</f>
+        <v/>
+      </c>
+      <c r="O15" s="19" t="n"/>
+      <c r="P15" s="14" t="n"/>
+    </row>
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="14">
-        <f>IFERROR(IF($B15="","",VLOOKUP($B15,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="14">
-        <f>IFERROR(IF($D15="","",VLOOKUP($D15,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="16" t="n"/>
-      <c r="H15" s="13" t="n"/>
-      <c r="I15" s="13" t="n"/>
-      <c r="J15" s="13" t="n"/>
-      <c r="K15" s="13" t="n"/>
-      <c r="L15" s="13" t="n"/>
-      <c r="M15" s="17">
-        <f>IF(OR($H15="",$L15=""),"",$H15-$L15)</f>
-        <v/>
-      </c>
-      <c r="N15" s="16" t="n"/>
-      <c r="O15" s="13" t="n"/>
-      <c r="P15" s="16" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" t="inlineStr">
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="21">
+        <f>IFERROR(IF($B16="","",VLOOKUP($B16,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="21">
+        <f>IFERROR(IF($D16="","",VLOOKUP($D16,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="22">
+        <f>IFERROR(IF($F16="","",VLOOKUP($F16,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="17" t="n"/>
+      <c r="I16" s="17" t="n"/>
+      <c r="J16" s="23">
+        <f>IF(AND($H16="",$I16=""),"",N($H16)+N($I16))</f>
+        <v/>
+      </c>
+      <c r="K16" s="14" t="n"/>
+      <c r="L16" s="19" t="n"/>
+      <c r="M16" s="17" t="n"/>
+      <c r="N16" s="24">
+        <f>IF(OR($J16="",$M16=""),"",$J16-$M16)</f>
+        <v/>
+      </c>
+      <c r="O16" s="19" t="n"/>
+      <c r="P16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="14">
-        <f>IFERROR(IF($B16="","",VLOOKUP($B16,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="14">
-        <f>IFERROR(IF($D16="","",VLOOKUP($D16,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="16" t="n"/>
-      <c r="H16" s="13" t="n"/>
-      <c r="I16" s="13" t="n"/>
-      <c r="J16" s="13" t="n"/>
-      <c r="K16" s="13" t="n"/>
-      <c r="L16" s="13" t="n"/>
-      <c r="M16" s="17">
-        <f>IF(OR($H16="",$L16=""),"",$H16-$L16)</f>
-        <v/>
-      </c>
-      <c r="N16" s="16" t="n"/>
-      <c r="O16" s="13" t="n"/>
-      <c r="P16" s="16" t="n"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" t="inlineStr">
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="15">
+        <f>IFERROR(IF($B17="","",VLOOKUP($B17,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="15">
+        <f>IFERROR(IF($D17="","",VLOOKUP($D17,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="16">
+        <f>IFERROR(IF($F17="","",VLOOKUP($F17,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="17" t="n"/>
+      <c r="I17" s="17" t="n"/>
+      <c r="J17" s="18">
+        <f>IF(AND($H17="",$I17=""),"",N($H17)+N($I17))</f>
+        <v/>
+      </c>
+      <c r="K17" s="14" t="n"/>
+      <c r="L17" s="19" t="n"/>
+      <c r="M17" s="17" t="n"/>
+      <c r="N17" s="20">
+        <f>IF(OR($J17="",$M17=""),"",$J17-$M17)</f>
+        <v/>
+      </c>
+      <c r="O17" s="19" t="n"/>
+      <c r="P17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="14">
-        <f>IFERROR(IF($B17="","",VLOOKUP($B17,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="14">
-        <f>IFERROR(IF($D17="","",VLOOKUP($D17,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="16" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="13" t="n"/>
-      <c r="L17" s="13" t="n"/>
-      <c r="M17" s="17">
-        <f>IF(OR($H17="",$L17=""),"",$H17-$L17)</f>
-        <v/>
-      </c>
-      <c r="N17" s="16" t="n"/>
-      <c r="O17" s="13" t="n"/>
-      <c r="P17" s="16" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" t="inlineStr">
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="21">
+        <f>IFERROR(IF($B18="","",VLOOKUP($B18,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="21">
+        <f>IFERROR(IF($D18="","",VLOOKUP($D18,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="22">
+        <f>IFERROR(IF($F18="","",VLOOKUP($F18,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="17" t="n"/>
+      <c r="I18" s="17" t="n"/>
+      <c r="J18" s="23">
+        <f>IF(AND($H18="",$I18=""),"",N($H18)+N($I18))</f>
+        <v/>
+      </c>
+      <c r="K18" s="14" t="n"/>
+      <c r="L18" s="19" t="n"/>
+      <c r="M18" s="17" t="n"/>
+      <c r="N18" s="24">
+        <f>IF(OR($J18="",$M18=""),"",$J18-$M18)</f>
+        <v/>
+      </c>
+      <c r="O18" s="19" t="n"/>
+      <c r="P18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="14">
-        <f>IFERROR(IF($B18="","",VLOOKUP($B18,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="14">
-        <f>IFERROR(IF($D18="","",VLOOKUP($D18,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="16" t="n"/>
-      <c r="H18" s="13" t="n"/>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="13" t="n"/>
-      <c r="L18" s="13" t="n"/>
-      <c r="M18" s="17">
-        <f>IF(OR($H18="",$L18=""),"",$H18-$L18)</f>
-        <v/>
-      </c>
-      <c r="N18" s="16" t="n"/>
-      <c r="O18" s="13" t="n"/>
-      <c r="P18" s="16" t="n"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" t="inlineStr">
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="15">
+        <f>IFERROR(IF($B19="","",VLOOKUP($B19,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="15">
+        <f>IFERROR(IF($D19="","",VLOOKUP($D19,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="16">
+        <f>IFERROR(IF($F19="","",VLOOKUP($F19,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="17" t="n"/>
+      <c r="I19" s="17" t="n"/>
+      <c r="J19" s="18">
+        <f>IF(AND($H19="",$I19=""),"",N($H19)+N($I19))</f>
+        <v/>
+      </c>
+      <c r="K19" s="14" t="n"/>
+      <c r="L19" s="19" t="n"/>
+      <c r="M19" s="17" t="n"/>
+      <c r="N19" s="20">
+        <f>IF(OR($J19="",$M19=""),"",$J19-$M19)</f>
+        <v/>
+      </c>
+      <c r="O19" s="19" t="n"/>
+      <c r="P19" s="14" t="n"/>
+    </row>
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="14">
-        <f>IFERROR(IF($B19="","",VLOOKUP($B19,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="14">
-        <f>IFERROR(IF($D19="","",VLOOKUP($D19,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="16" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
-      <c r="L19" s="13" t="n"/>
-      <c r="M19" s="17">
-        <f>IF(OR($H19="",$L19=""),"",$H19-$L19)</f>
-        <v/>
-      </c>
-      <c r="N19" s="16" t="n"/>
-      <c r="O19" s="13" t="n"/>
-      <c r="P19" s="16" t="n"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" t="inlineStr">
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="21">
+        <f>IFERROR(IF($B20="","",VLOOKUP($B20,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="21">
+        <f>IFERROR(IF($D20="","",VLOOKUP($D20,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="22">
+        <f>IFERROR(IF($F20="","",VLOOKUP($F20,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="17" t="n"/>
+      <c r="I20" s="17" t="n"/>
+      <c r="J20" s="23">
+        <f>IF(AND($H20="",$I20=""),"",N($H20)+N($I20))</f>
+        <v/>
+      </c>
+      <c r="K20" s="14" t="n"/>
+      <c r="L20" s="19" t="n"/>
+      <c r="M20" s="17" t="n"/>
+      <c r="N20" s="24">
+        <f>IF(OR($J20="",$M20=""),"",$J20-$M20)</f>
+        <v/>
+      </c>
+      <c r="O20" s="19" t="n"/>
+      <c r="P20" s="14" t="n"/>
+    </row>
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="14">
-        <f>IFERROR(IF($B20="","",VLOOKUP($B20,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="14">
-        <f>IFERROR(IF($D20="","",VLOOKUP($D20,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="16" t="n"/>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="13" t="n"/>
-      <c r="J20" s="13" t="n"/>
-      <c r="K20" s="13" t="n"/>
-      <c r="L20" s="13" t="n"/>
-      <c r="M20" s="17">
-        <f>IF(OR($H20="",$L20=""),"",$H20-$L20)</f>
-        <v/>
-      </c>
-      <c r="N20" s="16" t="n"/>
-      <c r="O20" s="13" t="n"/>
-      <c r="P20" s="16" t="n"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" t="inlineStr">
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="15">
+        <f>IFERROR(IF($B21="","",VLOOKUP($B21,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="15">
+        <f>IFERROR(IF($D21="","",VLOOKUP($D21,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="16">
+        <f>IFERROR(IF($F21="","",VLOOKUP($F21,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="17" t="n"/>
+      <c r="I21" s="17" t="n"/>
+      <c r="J21" s="18">
+        <f>IF(AND($H21="",$I21=""),"",N($H21)+N($I21))</f>
+        <v/>
+      </c>
+      <c r="K21" s="14" t="n"/>
+      <c r="L21" s="19" t="n"/>
+      <c r="M21" s="17" t="n"/>
+      <c r="N21" s="20">
+        <f>IF(OR($J21="",$M21=""),"",$J21-$M21)</f>
+        <v/>
+      </c>
+      <c r="O21" s="19" t="n"/>
+      <c r="P21" s="14" t="n"/>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="14">
-        <f>IFERROR(IF($B21="","",VLOOKUP($B21,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="14">
-        <f>IFERROR(IF($D21="","",VLOOKUP($D21,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="16" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="13" t="n"/>
-      <c r="L21" s="13" t="n"/>
-      <c r="M21" s="17">
-        <f>IF(OR($H21="",$L21=""),"",$H21-$L21)</f>
-        <v/>
-      </c>
-      <c r="N21" s="16" t="n"/>
-      <c r="O21" s="13" t="n"/>
-      <c r="P21" s="16" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" t="inlineStr">
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="21">
+        <f>IFERROR(IF($B22="","",VLOOKUP($B22,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="21">
+        <f>IFERROR(IF($D22="","",VLOOKUP($D22,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="22">
+        <f>IFERROR(IF($F22="","",VLOOKUP($F22,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="17" t="n"/>
+      <c r="I22" s="17" t="n"/>
+      <c r="J22" s="23">
+        <f>IF(AND($H22="",$I22=""),"",N($H22)+N($I22))</f>
+        <v/>
+      </c>
+      <c r="K22" s="14" t="n"/>
+      <c r="L22" s="19" t="n"/>
+      <c r="M22" s="17" t="n"/>
+      <c r="N22" s="24">
+        <f>IF(OR($J22="",$M22=""),"",$J22-$M22)</f>
+        <v/>
+      </c>
+      <c r="O22" s="19" t="n"/>
+      <c r="P22" s="14" t="n"/>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="14">
-        <f>IFERROR(IF($B22="","",VLOOKUP($B22,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="14">
-        <f>IFERROR(IF($D22="","",VLOOKUP($D22,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="16" t="n"/>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="13" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="13" t="n"/>
-      <c r="L22" s="13" t="n"/>
-      <c r="M22" s="17">
-        <f>IF(OR($H22="",$L22=""),"",$H22-$L22)</f>
-        <v/>
-      </c>
-      <c r="N22" s="16" t="n"/>
-      <c r="O22" s="13" t="n"/>
-      <c r="P22" s="16" t="n"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" t="inlineStr">
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="15">
+        <f>IFERROR(IF($B23="","",VLOOKUP($B23,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="15">
+        <f>IFERROR(IF($D23="","",VLOOKUP($D23,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="16">
+        <f>IFERROR(IF($F23="","",VLOOKUP($F23,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="17" t="n"/>
+      <c r="I23" s="17" t="n"/>
+      <c r="J23" s="18">
+        <f>IF(AND($H23="",$I23=""),"",N($H23)+N($I23))</f>
+        <v/>
+      </c>
+      <c r="K23" s="14" t="n"/>
+      <c r="L23" s="19" t="n"/>
+      <c r="M23" s="17" t="n"/>
+      <c r="N23" s="20">
+        <f>IF(OR($J23="",$M23=""),"",$J23-$M23)</f>
+        <v/>
+      </c>
+      <c r="O23" s="19" t="n"/>
+      <c r="P23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="14">
-        <f>IFERROR(IF($B23="","",VLOOKUP($B23,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="14">
-        <f>IFERROR(IF($D23="","",VLOOKUP($D23,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="16" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="13" t="n"/>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="13" t="n"/>
-      <c r="L23" s="13" t="n"/>
-      <c r="M23" s="17">
-        <f>IF(OR($H23="",$L23=""),"",$H23-$L23)</f>
-        <v/>
-      </c>
-      <c r="N23" s="16" t="n"/>
-      <c r="O23" s="13" t="n"/>
-      <c r="P23" s="16" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" t="inlineStr">
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="21">
+        <f>IFERROR(IF($B24="","",VLOOKUP($B24,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="21">
+        <f>IFERROR(IF($D24="","",VLOOKUP($D24,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="22">
+        <f>IFERROR(IF($F24="","",VLOOKUP($F24,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="17" t="n"/>
+      <c r="I24" s="17" t="n"/>
+      <c r="J24" s="23">
+        <f>IF(AND($H24="",$I24=""),"",N($H24)+N($I24))</f>
+        <v/>
+      </c>
+      <c r="K24" s="14" t="n"/>
+      <c r="L24" s="19" t="n"/>
+      <c r="M24" s="17" t="n"/>
+      <c r="N24" s="24">
+        <f>IF(OR($J24="",$M24=""),"",$J24-$M24)</f>
+        <v/>
+      </c>
+      <c r="O24" s="19" t="n"/>
+      <c r="P24" s="14" t="n"/>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="14">
-        <f>IFERROR(IF($B24="","",VLOOKUP($B24,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="14">
-        <f>IFERROR(IF($D24="","",VLOOKUP($D24,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="16" t="n"/>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="13" t="n"/>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="13" t="n"/>
-      <c r="L24" s="13" t="n"/>
-      <c r="M24" s="17">
-        <f>IF(OR($H24="",$L24=""),"",$H24-$L24)</f>
-        <v/>
-      </c>
-      <c r="N24" s="16" t="n"/>
-      <c r="O24" s="13" t="n"/>
-      <c r="P24" s="16" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" t="inlineStr">
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="15">
+        <f>IFERROR(IF($B25="","",VLOOKUP($B25,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="15">
+        <f>IFERROR(IF($D25="","",VLOOKUP($D25,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="16">
+        <f>IFERROR(IF($F25="","",VLOOKUP($F25,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="17" t="n"/>
+      <c r="I25" s="17" t="n"/>
+      <c r="J25" s="18">
+        <f>IF(AND($H25="",$I25=""),"",N($H25)+N($I25))</f>
+        <v/>
+      </c>
+      <c r="K25" s="14" t="n"/>
+      <c r="L25" s="19" t="n"/>
+      <c r="M25" s="17" t="n"/>
+      <c r="N25" s="20">
+        <f>IF(OR($J25="",$M25=""),"",$J25-$M25)</f>
+        <v/>
+      </c>
+      <c r="O25" s="19" t="n"/>
+      <c r="P25" s="14" t="n"/>
+    </row>
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="14">
-        <f>IFERROR(IF($B25="","",VLOOKUP($B25,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="14">
-        <f>IFERROR(IF($D25="","",VLOOKUP($D25,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F25" s="13" t="n"/>
-      <c r="G25" s="16" t="n"/>
-      <c r="H25" s="13" t="n"/>
-      <c r="I25" s="13" t="n"/>
-      <c r="J25" s="13" t="n"/>
-      <c r="K25" s="13" t="n"/>
-      <c r="L25" s="13" t="n"/>
-      <c r="M25" s="17">
-        <f>IF(OR($H25="",$L25=""),"",$H25-$L25)</f>
-        <v/>
-      </c>
-      <c r="N25" s="16" t="n"/>
-      <c r="O25" s="13" t="n"/>
-      <c r="P25" s="16" t="n"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" t="inlineStr">
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="21">
+        <f>IFERROR(IF($B26="","",VLOOKUP($B26,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="21">
+        <f>IFERROR(IF($D26="","",VLOOKUP($D26,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="22">
+        <f>IFERROR(IF($F26="","",VLOOKUP($F26,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="17" t="n"/>
+      <c r="I26" s="17" t="n"/>
+      <c r="J26" s="23">
+        <f>IF(AND($H26="",$I26=""),"",N($H26)+N($I26))</f>
+        <v/>
+      </c>
+      <c r="K26" s="14" t="n"/>
+      <c r="L26" s="19" t="n"/>
+      <c r="M26" s="17" t="n"/>
+      <c r="N26" s="24">
+        <f>IF(OR($J26="",$M26=""),"",$J26-$M26)</f>
+        <v/>
+      </c>
+      <c r="O26" s="19" t="n"/>
+      <c r="P26" s="14" t="n"/>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="14">
-        <f>IFERROR(IF($B26="","",VLOOKUP($B26,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="14">
-        <f>IFERROR(IF($D26="","",VLOOKUP($D26,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="16" t="n"/>
-      <c r="H26" s="13" t="n"/>
-      <c r="I26" s="13" t="n"/>
-      <c r="J26" s="13" t="n"/>
-      <c r="K26" s="13" t="n"/>
-      <c r="L26" s="13" t="n"/>
-      <c r="M26" s="17">
-        <f>IF(OR($H26="",$L26=""),"",$H26-$L26)</f>
-        <v/>
-      </c>
-      <c r="N26" s="16" t="n"/>
-      <c r="O26" s="13" t="n"/>
-      <c r="P26" s="16" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" t="inlineStr">
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="15">
+        <f>IFERROR(IF($B27="","",VLOOKUP($B27,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="15">
+        <f>IFERROR(IF($D27="","",VLOOKUP($D27,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="16">
+        <f>IFERROR(IF($F27="","",VLOOKUP($F27,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="17" t="n"/>
+      <c r="I27" s="17" t="n"/>
+      <c r="J27" s="18">
+        <f>IF(AND($H27="",$I27=""),"",N($H27)+N($I27))</f>
+        <v/>
+      </c>
+      <c r="K27" s="14" t="n"/>
+      <c r="L27" s="19" t="n"/>
+      <c r="M27" s="17" t="n"/>
+      <c r="N27" s="20">
+        <f>IF(OR($J27="",$M27=""),"",$J27-$M27)</f>
+        <v/>
+      </c>
+      <c r="O27" s="19" t="n"/>
+      <c r="P27" s="14" t="n"/>
+    </row>
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="14">
-        <f>IFERROR(IF($B27="","",VLOOKUP($B27,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="14">
-        <f>IFERROR(IF($D27="","",VLOOKUP($D27,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="16" t="n"/>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="13" t="n"/>
-      <c r="J27" s="13" t="n"/>
-      <c r="K27" s="13" t="n"/>
-      <c r="L27" s="13" t="n"/>
-      <c r="M27" s="17">
-        <f>IF(OR($H27="",$L27=""),"",$H27-$L27)</f>
-        <v/>
-      </c>
-      <c r="N27" s="16" t="n"/>
-      <c r="O27" s="13" t="n"/>
-      <c r="P27" s="16" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" t="inlineStr">
+      <c r="B28" s="14" t="n"/>
+      <c r="C28" s="21">
+        <f>IFERROR(IF($B28="","",VLOOKUP($B28,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="21">
+        <f>IFERROR(IF($D28="","",VLOOKUP($D28,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="22">
+        <f>IFERROR(IF($F28="","",VLOOKUP($F28,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="17" t="n"/>
+      <c r="I28" s="17" t="n"/>
+      <c r="J28" s="23">
+        <f>IF(AND($H28="",$I28=""),"",N($H28)+N($I28))</f>
+        <v/>
+      </c>
+      <c r="K28" s="14" t="n"/>
+      <c r="L28" s="19" t="n"/>
+      <c r="M28" s="17" t="n"/>
+      <c r="N28" s="24">
+        <f>IF(OR($J28="",$M28=""),"",$J28-$M28)</f>
+        <v/>
+      </c>
+      <c r="O28" s="19" t="n"/>
+      <c r="P28" s="14" t="n"/>
+    </row>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="14">
-        <f>IFERROR(IF($B28="","",VLOOKUP($B28,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="14">
-        <f>IFERROR(IF($D28="","",VLOOKUP($D28,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="16" t="n"/>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="13" t="n"/>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="13" t="n"/>
-      <c r="L28" s="13" t="n"/>
-      <c r="M28" s="17">
-        <f>IF(OR($H28="",$L28=""),"",$H28-$L28)</f>
-        <v/>
-      </c>
-      <c r="N28" s="16" t="n"/>
-      <c r="O28" s="13" t="n"/>
-      <c r="P28" s="16" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" t="inlineStr">
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="15">
+        <f>IFERROR(IF($B29="","",VLOOKUP($B29,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="15">
+        <f>IFERROR(IF($D29="","",VLOOKUP($D29,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="16">
+        <f>IFERROR(IF($F29="","",VLOOKUP($F29,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="17" t="n"/>
+      <c r="J29" s="18">
+        <f>IF(AND($H29="",$I29=""),"",N($H29)+N($I29))</f>
+        <v/>
+      </c>
+      <c r="K29" s="14" t="n"/>
+      <c r="L29" s="19" t="n"/>
+      <c r="M29" s="17" t="n"/>
+      <c r="N29" s="20">
+        <f>IF(OR($J29="",$M29=""),"",$J29-$M29)</f>
+        <v/>
+      </c>
+      <c r="O29" s="19" t="n"/>
+      <c r="P29" s="14" t="n"/>
+    </row>
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="14">
-        <f>IFERROR(IF($B29="","",VLOOKUP($B29,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="14">
-        <f>IFERROR(IF($D29="","",VLOOKUP($D29,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="16" t="n"/>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="13" t="n"/>
-      <c r="J29" s="13" t="n"/>
-      <c r="K29" s="13" t="n"/>
-      <c r="L29" s="13" t="n"/>
-      <c r="M29" s="17">
-        <f>IF(OR($H29="",$L29=""),"",$H29-$L29)</f>
-        <v/>
-      </c>
-      <c r="N29" s="16" t="n"/>
-      <c r="O29" s="13" t="n"/>
-      <c r="P29" s="16" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" t="inlineStr">
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="21">
+        <f>IFERROR(IF($B30="","",VLOOKUP($B30,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="21">
+        <f>IFERROR(IF($D30="","",VLOOKUP($D30,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="22">
+        <f>IFERROR(IF($F30="","",VLOOKUP($F30,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="17" t="n"/>
+      <c r="I30" s="17" t="n"/>
+      <c r="J30" s="23">
+        <f>IF(AND($H30="",$I30=""),"",N($H30)+N($I30))</f>
+        <v/>
+      </c>
+      <c r="K30" s="14" t="n"/>
+      <c r="L30" s="19" t="n"/>
+      <c r="M30" s="17" t="n"/>
+      <c r="N30" s="24">
+        <f>IF(OR($J30="",$M30=""),"",$J30-$M30)</f>
+        <v/>
+      </c>
+      <c r="O30" s="19" t="n"/>
+      <c r="P30" s="14" t="n"/>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="14">
-        <f>IFERROR(IF($B30="","",VLOOKUP($B30,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D30" s="15" t="n"/>
-      <c r="E30" s="14">
-        <f>IFERROR(IF($D30="","",VLOOKUP($D30,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="16" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="13" t="n"/>
-      <c r="L30" s="13" t="n"/>
-      <c r="M30" s="17">
-        <f>IF(OR($H30="",$L30=""),"",$H30-$L30)</f>
-        <v/>
-      </c>
-      <c r="N30" s="16" t="n"/>
-      <c r="O30" s="13" t="n"/>
-      <c r="P30" s="16" t="n"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" t="inlineStr">
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="15">
+        <f>IFERROR(IF($B31="","",VLOOKUP($B31,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="15">
+        <f>IFERROR(IF($D31="","",VLOOKUP($D31,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="16">
+        <f>IFERROR(IF($F31="","",VLOOKUP($F31,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="17" t="n"/>
+      <c r="I31" s="17" t="n"/>
+      <c r="J31" s="18">
+        <f>IF(AND($H31="",$I31=""),"",N($H31)+N($I31))</f>
+        <v/>
+      </c>
+      <c r="K31" s="14" t="n"/>
+      <c r="L31" s="19" t="n"/>
+      <c r="M31" s="17" t="n"/>
+      <c r="N31" s="20">
+        <f>IF(OR($J31="",$M31=""),"",$J31-$M31)</f>
+        <v/>
+      </c>
+      <c r="O31" s="19" t="n"/>
+      <c r="P31" s="14" t="n"/>
+    </row>
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="14">
-        <f>IFERROR(IF($B31="","",VLOOKUP($B31,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D31" s="15" t="n"/>
-      <c r="E31" s="14">
-        <f>IFERROR(IF($D31="","",VLOOKUP($D31,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="16" t="n"/>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="13" t="n"/>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="13" t="n"/>
-      <c r="L31" s="13" t="n"/>
-      <c r="M31" s="17">
-        <f>IF(OR($H31="",$L31=""),"",$H31-$L31)</f>
-        <v/>
-      </c>
-      <c r="N31" s="16" t="n"/>
-      <c r="O31" s="13" t="n"/>
-      <c r="P31" s="16" t="n"/>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" t="inlineStr">
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="21">
+        <f>IFERROR(IF($B32="","",VLOOKUP($B32,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="21">
+        <f>IFERROR(IF($D32="","",VLOOKUP($D32,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="22">
+        <f>IFERROR(IF($F32="","",VLOOKUP($F32,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="17" t="n"/>
+      <c r="I32" s="17" t="n"/>
+      <c r="J32" s="23">
+        <f>IF(AND($H32="",$I32=""),"",N($H32)+N($I32))</f>
+        <v/>
+      </c>
+      <c r="K32" s="14" t="n"/>
+      <c r="L32" s="19" t="n"/>
+      <c r="M32" s="17" t="n"/>
+      <c r="N32" s="24">
+        <f>IF(OR($J32="",$M32=""),"",$J32-$M32)</f>
+        <v/>
+      </c>
+      <c r="O32" s="19" t="n"/>
+      <c r="P32" s="14" t="n"/>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="14">
-        <f>IFERROR(IF($B32="","",VLOOKUP($B32,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D32" s="15" t="n"/>
-      <c r="E32" s="14">
-        <f>IFERROR(IF($D32="","",VLOOKUP($D32,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="16" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="13" t="n"/>
-      <c r="J32" s="13" t="n"/>
-      <c r="K32" s="13" t="n"/>
-      <c r="L32" s="13" t="n"/>
-      <c r="M32" s="17">
-        <f>IF(OR($H32="",$L32=""),"",$H32-$L32)</f>
-        <v/>
-      </c>
-      <c r="N32" s="16" t="n"/>
-      <c r="O32" s="13" t="n"/>
-      <c r="P32" s="16" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" t="inlineStr">
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="15">
+        <f>IFERROR(IF($B33="","",VLOOKUP($B33,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="15">
+        <f>IFERROR(IF($D33="","",VLOOKUP($D33,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="16">
+        <f>IFERROR(IF($F33="","",VLOOKUP($F33,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="17" t="n"/>
+      <c r="I33" s="17" t="n"/>
+      <c r="J33" s="18">
+        <f>IF(AND($H33="",$I33=""),"",N($H33)+N($I33))</f>
+        <v/>
+      </c>
+      <c r="K33" s="14" t="n"/>
+      <c r="L33" s="19" t="n"/>
+      <c r="M33" s="17" t="n"/>
+      <c r="N33" s="20">
+        <f>IF(OR($J33="",$M33=""),"",$J33-$M33)</f>
+        <v/>
+      </c>
+      <c r="O33" s="19" t="n"/>
+      <c r="P33" s="14" t="n"/>
+    </row>
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="14">
-        <f>IFERROR(IF($B33="","",VLOOKUP($B33,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D33" s="15" t="n"/>
-      <c r="E33" s="14">
-        <f>IFERROR(IF($D33="","",VLOOKUP($D33,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="16" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="13" t="n"/>
-      <c r="J33" s="13" t="n"/>
-      <c r="K33" s="13" t="n"/>
-      <c r="L33" s="13" t="n"/>
-      <c r="M33" s="17">
-        <f>IF(OR($H33="",$L33=""),"",$H33-$L33)</f>
-        <v/>
-      </c>
-      <c r="N33" s="16" t="n"/>
-      <c r="O33" s="13" t="n"/>
-      <c r="P33" s="16" t="n"/>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" t="inlineStr">
+      <c r="B34" s="14" t="n"/>
+      <c r="C34" s="21">
+        <f>IFERROR(IF($B34="","",VLOOKUP($B34,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="21">
+        <f>IFERROR(IF($D34="","",VLOOKUP($D34,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="22">
+        <f>IFERROR(IF($F34="","",VLOOKUP($F34,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="17" t="n"/>
+      <c r="I34" s="17" t="n"/>
+      <c r="J34" s="23">
+        <f>IF(AND($H34="",$I34=""),"",N($H34)+N($I34))</f>
+        <v/>
+      </c>
+      <c r="K34" s="14" t="n"/>
+      <c r="L34" s="19" t="n"/>
+      <c r="M34" s="17" t="n"/>
+      <c r="N34" s="24">
+        <f>IF(OR($J34="",$M34=""),"",$J34-$M34)</f>
+        <v/>
+      </c>
+      <c r="O34" s="19" t="n"/>
+      <c r="P34" s="14" t="n"/>
+    </row>
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="14">
-        <f>IFERROR(IF($B34="","",VLOOKUP($B34,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D34" s="15" t="n"/>
-      <c r="E34" s="14">
-        <f>IFERROR(IF($D34="","",VLOOKUP($D34,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="16" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="13" t="n"/>
-      <c r="L34" s="13" t="n"/>
-      <c r="M34" s="17">
-        <f>IF(OR($H34="",$L34=""),"",$H34-$L34)</f>
-        <v/>
-      </c>
-      <c r="N34" s="16" t="n"/>
-      <c r="O34" s="13" t="n"/>
-      <c r="P34" s="16" t="n"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" t="inlineStr">
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="15">
+        <f>IFERROR(IF($B35="","",VLOOKUP($B35,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="15">
+        <f>IFERROR(IF($D35="","",VLOOKUP($D35,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="16">
+        <f>IFERROR(IF($F35="","",VLOOKUP($F35,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="17" t="n"/>
+      <c r="I35" s="17" t="n"/>
+      <c r="J35" s="18">
+        <f>IF(AND($H35="",$I35=""),"",N($H35)+N($I35))</f>
+        <v/>
+      </c>
+      <c r="K35" s="14" t="n"/>
+      <c r="L35" s="19" t="n"/>
+      <c r="M35" s="17" t="n"/>
+      <c r="N35" s="20">
+        <f>IF(OR($J35="",$M35=""),"",$J35-$M35)</f>
+        <v/>
+      </c>
+      <c r="O35" s="19" t="n"/>
+      <c r="P35" s="14" t="n"/>
+    </row>
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="14">
-        <f>IFERROR(IF($B35="","",VLOOKUP($B35,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="14">
-        <f>IFERROR(IF($D35="","",VLOOKUP($D35,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="16" t="n"/>
-      <c r="H35" s="13" t="n"/>
-      <c r="I35" s="13" t="n"/>
-      <c r="J35" s="13" t="n"/>
-      <c r="K35" s="13" t="n"/>
-      <c r="L35" s="13" t="n"/>
-      <c r="M35" s="17">
-        <f>IF(OR($H35="",$L35=""),"",$H35-$L35)</f>
-        <v/>
-      </c>
-      <c r="N35" s="16" t="n"/>
-      <c r="O35" s="13" t="n"/>
-      <c r="P35" s="16" t="n"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" t="inlineStr">
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="21">
+        <f>IFERROR(IF($B36="","",VLOOKUP($B36,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="21">
+        <f>IFERROR(IF($D36="","",VLOOKUP($D36,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="22">
+        <f>IFERROR(IF($F36="","",VLOOKUP($F36,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="17" t="n"/>
+      <c r="I36" s="17" t="n"/>
+      <c r="J36" s="23">
+        <f>IF(AND($H36="",$I36=""),"",N($H36)+N($I36))</f>
+        <v/>
+      </c>
+      <c r="K36" s="14" t="n"/>
+      <c r="L36" s="19" t="n"/>
+      <c r="M36" s="17" t="n"/>
+      <c r="N36" s="24">
+        <f>IF(OR($J36="",$M36=""),"",$J36-$M36)</f>
+        <v/>
+      </c>
+      <c r="O36" s="19" t="n"/>
+      <c r="P36" s="14" t="n"/>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="14">
-        <f>IFERROR(IF($B36="","",VLOOKUP($B36,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="14">
-        <f>IFERROR(IF($D36="","",VLOOKUP($D36,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="16" t="n"/>
-      <c r="H36" s="13" t="n"/>
-      <c r="I36" s="13" t="n"/>
-      <c r="J36" s="13" t="n"/>
-      <c r="K36" s="13" t="n"/>
-      <c r="L36" s="13" t="n"/>
-      <c r="M36" s="17">
-        <f>IF(OR($H36="",$L36=""),"",$H36-$L36)</f>
-        <v/>
-      </c>
-      <c r="N36" s="16" t="n"/>
-      <c r="O36" s="13" t="n"/>
-      <c r="P36" s="16" t="n"/>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" t="inlineStr">
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="15">
+        <f>IFERROR(IF($B37="","",VLOOKUP($B37,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="15">
+        <f>IFERROR(IF($D37="","",VLOOKUP($D37,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="16">
+        <f>IFERROR(IF($F37="","",VLOOKUP($F37,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="17" t="n"/>
+      <c r="I37" s="17" t="n"/>
+      <c r="J37" s="18">
+        <f>IF(AND($H37="",$I37=""),"",N($H37)+N($I37))</f>
+        <v/>
+      </c>
+      <c r="K37" s="14" t="n"/>
+      <c r="L37" s="19" t="n"/>
+      <c r="M37" s="17" t="n"/>
+      <c r="N37" s="20">
+        <f>IF(OR($J37="",$M37=""),"",$J37-$M37)</f>
+        <v/>
+      </c>
+      <c r="O37" s="19" t="n"/>
+      <c r="P37" s="14" t="n"/>
+    </row>
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="14">
-        <f>IFERROR(IF($B37="","",VLOOKUP($B37,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D37" s="15" t="n"/>
-      <c r="E37" s="14">
-        <f>IFERROR(IF($D37="","",VLOOKUP($D37,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="16" t="n"/>
-      <c r="H37" s="13" t="n"/>
-      <c r="I37" s="13" t="n"/>
-      <c r="J37" s="13" t="n"/>
-      <c r="K37" s="13" t="n"/>
-      <c r="L37" s="13" t="n"/>
-      <c r="M37" s="17">
-        <f>IF(OR($H37="",$L37=""),"",$H37-$L37)</f>
-        <v/>
-      </c>
-      <c r="N37" s="16" t="n"/>
-      <c r="O37" s="13" t="n"/>
-      <c r="P37" s="16" t="n"/>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" t="inlineStr">
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="21">
+        <f>IFERROR(IF($B38="","",VLOOKUP($B38,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="21">
+        <f>IFERROR(IF($D38="","",VLOOKUP($D38,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F38" s="14" t="n"/>
+      <c r="G38" s="22">
+        <f>IFERROR(IF($F38="","",VLOOKUP($F38,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="17" t="n"/>
+      <c r="I38" s="17" t="n"/>
+      <c r="J38" s="23">
+        <f>IF(AND($H38="",$I38=""),"",N($H38)+N($I38))</f>
+        <v/>
+      </c>
+      <c r="K38" s="14" t="n"/>
+      <c r="L38" s="19" t="n"/>
+      <c r="M38" s="17" t="n"/>
+      <c r="N38" s="24">
+        <f>IF(OR($J38="",$M38=""),"",$J38-$M38)</f>
+        <v/>
+      </c>
+      <c r="O38" s="19" t="n"/>
+      <c r="P38" s="14" t="n"/>
+    </row>
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="14">
-        <f>IFERROR(IF($B38="","",VLOOKUP($B38,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D38" s="15" t="n"/>
-      <c r="E38" s="14">
-        <f>IFERROR(IF($D38="","",VLOOKUP($D38,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="16" t="n"/>
-      <c r="H38" s="13" t="n"/>
-      <c r="I38" s="13" t="n"/>
-      <c r="J38" s="13" t="n"/>
-      <c r="K38" s="13" t="n"/>
-      <c r="L38" s="13" t="n"/>
-      <c r="M38" s="17">
-        <f>IF(OR($H38="",$L38=""),"",$H38-$L38)</f>
-        <v/>
-      </c>
-      <c r="N38" s="16" t="n"/>
-      <c r="O38" s="13" t="n"/>
-      <c r="P38" s="16" t="n"/>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" t="inlineStr">
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="15">
+        <f>IFERROR(IF($B39="","",VLOOKUP($B39,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="15">
+        <f>IFERROR(IF($D39="","",VLOOKUP($D39,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F39" s="14" t="n"/>
+      <c r="G39" s="16">
+        <f>IFERROR(IF($F39="","",VLOOKUP($F39,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="17" t="n"/>
+      <c r="I39" s="17" t="n"/>
+      <c r="J39" s="18">
+        <f>IF(AND($H39="",$I39=""),"",N($H39)+N($I39))</f>
+        <v/>
+      </c>
+      <c r="K39" s="14" t="n"/>
+      <c r="L39" s="19" t="n"/>
+      <c r="M39" s="17" t="n"/>
+      <c r="N39" s="20">
+        <f>IF(OR($J39="",$M39=""),"",$J39-$M39)</f>
+        <v/>
+      </c>
+      <c r="O39" s="19" t="n"/>
+      <c r="P39" s="14" t="n"/>
+    </row>
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B39" s="13" t="n"/>
-      <c r="C39" s="14">
-        <f>IFERROR(IF($B39="","",VLOOKUP($B39,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D39" s="15" t="n"/>
-      <c r="E39" s="14">
-        <f>IFERROR(IF($D39="","",VLOOKUP($D39,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="16" t="n"/>
-      <c r="H39" s="13" t="n"/>
-      <c r="I39" s="13" t="n"/>
-      <c r="J39" s="13" t="n"/>
-      <c r="K39" s="13" t="n"/>
-      <c r="L39" s="13" t="n"/>
-      <c r="M39" s="17">
-        <f>IF(OR($H39="",$L39=""),"",$H39-$L39)</f>
-        <v/>
-      </c>
-      <c r="N39" s="16" t="n"/>
-      <c r="O39" s="13" t="n"/>
-      <c r="P39" s="16" t="n"/>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" t="inlineStr">
+      <c r="B40" s="14" t="n"/>
+      <c r="C40" s="21">
+        <f>IFERROR(IF($B40="","",VLOOKUP($B40,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D40" s="14" t="n"/>
+      <c r="E40" s="21">
+        <f>IFERROR(IF($D40="","",VLOOKUP($D40,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F40" s="14" t="n"/>
+      <c r="G40" s="22">
+        <f>IFERROR(IF($F40="","",VLOOKUP($F40,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="17" t="n"/>
+      <c r="I40" s="17" t="n"/>
+      <c r="J40" s="23">
+        <f>IF(AND($H40="",$I40=""),"",N($H40)+N($I40))</f>
+        <v/>
+      </c>
+      <c r="K40" s="14" t="n"/>
+      <c r="L40" s="19" t="n"/>
+      <c r="M40" s="17" t="n"/>
+      <c r="N40" s="24">
+        <f>IF(OR($J40="",$M40=""),"",$J40-$M40)</f>
+        <v/>
+      </c>
+      <c r="O40" s="19" t="n"/>
+      <c r="P40" s="14" t="n"/>
+    </row>
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B40" s="13" t="n"/>
-      <c r="C40" s="14">
-        <f>IFERROR(IF($B40="","",VLOOKUP($B40,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D40" s="15" t="n"/>
-      <c r="E40" s="14">
-        <f>IFERROR(IF($D40="","",VLOOKUP($D40,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="16" t="n"/>
-      <c r="H40" s="13" t="n"/>
-      <c r="I40" s="13" t="n"/>
-      <c r="J40" s="13" t="n"/>
-      <c r="K40" s="13" t="n"/>
-      <c r="L40" s="13" t="n"/>
-      <c r="M40" s="17">
-        <f>IF(OR($H40="",$L40=""),"",$H40-$L40)</f>
-        <v/>
-      </c>
-      <c r="N40" s="16" t="n"/>
-      <c r="O40" s="13" t="n"/>
-      <c r="P40" s="16" t="n"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" t="inlineStr">
+      <c r="B41" s="14" t="n"/>
+      <c r="C41" s="15">
+        <f>IFERROR(IF($B41="","",VLOOKUP($B41,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D41" s="14" t="n"/>
+      <c r="E41" s="15">
+        <f>IFERROR(IF($D41="","",VLOOKUP($D41,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F41" s="14" t="n"/>
+      <c r="G41" s="16">
+        <f>IFERROR(IF($F41="","",VLOOKUP($F41,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="17" t="n"/>
+      <c r="I41" s="17" t="n"/>
+      <c r="J41" s="18">
+        <f>IF(AND($H41="",$I41=""),"",N($H41)+N($I41))</f>
+        <v/>
+      </c>
+      <c r="K41" s="14" t="n"/>
+      <c r="L41" s="19" t="n"/>
+      <c r="M41" s="17" t="n"/>
+      <c r="N41" s="20">
+        <f>IF(OR($J41="",$M41=""),"",$J41-$M41)</f>
+        <v/>
+      </c>
+      <c r="O41" s="19" t="n"/>
+      <c r="P41" s="14" t="n"/>
+    </row>
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B41" s="13" t="n"/>
-      <c r="C41" s="14">
-        <f>IFERROR(IF($B41="","",VLOOKUP($B41,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D41" s="15" t="n"/>
-      <c r="E41" s="14">
-        <f>IFERROR(IF($D41="","",VLOOKUP($D41,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="16" t="n"/>
-      <c r="H41" s="13" t="n"/>
-      <c r="I41" s="13" t="n"/>
-      <c r="J41" s="13" t="n"/>
-      <c r="K41" s="13" t="n"/>
-      <c r="L41" s="13" t="n"/>
-      <c r="M41" s="17">
-        <f>IF(OR($H41="",$L41=""),"",$H41-$L41)</f>
-        <v/>
-      </c>
-      <c r="N41" s="16" t="n"/>
-      <c r="O41" s="13" t="n"/>
-      <c r="P41" s="16" t="n"/>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" t="inlineStr">
+      <c r="B42" s="14" t="n"/>
+      <c r="C42" s="21">
+        <f>IFERROR(IF($B42="","",VLOOKUP($B42,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D42" s="14" t="n"/>
+      <c r="E42" s="21">
+        <f>IFERROR(IF($D42="","",VLOOKUP($D42,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F42" s="14" t="n"/>
+      <c r="G42" s="22">
+        <f>IFERROR(IF($F42="","",VLOOKUP($F42,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="17" t="n"/>
+      <c r="I42" s="17" t="n"/>
+      <c r="J42" s="23">
+        <f>IF(AND($H42="",$I42=""),"",N($H42)+N($I42))</f>
+        <v/>
+      </c>
+      <c r="K42" s="14" t="n"/>
+      <c r="L42" s="19" t="n"/>
+      <c r="M42" s="17" t="n"/>
+      <c r="N42" s="24">
+        <f>IF(OR($J42="",$M42=""),"",$J42-$M42)</f>
+        <v/>
+      </c>
+      <c r="O42" s="19" t="n"/>
+      <c r="P42" s="14" t="n"/>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B42" s="13" t="n"/>
-      <c r="C42" s="14">
-        <f>IFERROR(IF($B42="","",VLOOKUP($B42,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D42" s="15" t="n"/>
-      <c r="E42" s="14">
-        <f>IFERROR(IF($D42="","",VLOOKUP($D42,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="16" t="n"/>
-      <c r="H42" s="13" t="n"/>
-      <c r="I42" s="13" t="n"/>
-      <c r="J42" s="13" t="n"/>
-      <c r="K42" s="13" t="n"/>
-      <c r="L42" s="13" t="n"/>
-      <c r="M42" s="17">
-        <f>IF(OR($H42="",$L42=""),"",$H42-$L42)</f>
-        <v/>
-      </c>
-      <c r="N42" s="16" t="n"/>
-      <c r="O42" s="13" t="n"/>
-      <c r="P42" s="16" t="n"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" t="inlineStr">
+      <c r="B43" s="14" t="n"/>
+      <c r="C43" s="15">
+        <f>IFERROR(IF($B43="","",VLOOKUP($B43,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D43" s="14" t="n"/>
+      <c r="E43" s="15">
+        <f>IFERROR(IF($D43="","",VLOOKUP($D43,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F43" s="14" t="n"/>
+      <c r="G43" s="16">
+        <f>IFERROR(IF($F43="","",VLOOKUP($F43,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="17" t="n"/>
+      <c r="I43" s="17" t="n"/>
+      <c r="J43" s="18">
+        <f>IF(AND($H43="",$I43=""),"",N($H43)+N($I43))</f>
+        <v/>
+      </c>
+      <c r="K43" s="14" t="n"/>
+      <c r="L43" s="19" t="n"/>
+      <c r="M43" s="17" t="n"/>
+      <c r="N43" s="20">
+        <f>IF(OR($J43="",$M43=""),"",$J43-$M43)</f>
+        <v/>
+      </c>
+      <c r="O43" s="19" t="n"/>
+      <c r="P43" s="14" t="n"/>
+    </row>
+    <row r="44" ht="19" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B43" s="13" t="n"/>
-      <c r="C43" s="14">
-        <f>IFERROR(IF($B43="","",VLOOKUP($B43,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D43" s="15" t="n"/>
-      <c r="E43" s="14">
-        <f>IFERROR(IF($D43="","",VLOOKUP($D43,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F43" s="13" t="n"/>
-      <c r="G43" s="16" t="n"/>
-      <c r="H43" s="13" t="n"/>
-      <c r="I43" s="13" t="n"/>
-      <c r="J43" s="13" t="n"/>
-      <c r="K43" s="13" t="n"/>
-      <c r="L43" s="13" t="n"/>
-      <c r="M43" s="17">
-        <f>IF(OR($H43="",$L43=""),"",$H43-$L43)</f>
-        <v/>
-      </c>
-      <c r="N43" s="16" t="n"/>
-      <c r="O43" s="13" t="n"/>
-      <c r="P43" s="16" t="n"/>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" t="inlineStr">
+      <c r="B44" s="14" t="n"/>
+      <c r="C44" s="21">
+        <f>IFERROR(IF($B44="","",VLOOKUP($B44,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D44" s="14" t="n"/>
+      <c r="E44" s="21">
+        <f>IFERROR(IF($D44="","",VLOOKUP($D44,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F44" s="14" t="n"/>
+      <c r="G44" s="22">
+        <f>IFERROR(IF($F44="","",VLOOKUP($F44,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="17" t="n"/>
+      <c r="I44" s="17" t="n"/>
+      <c r="J44" s="23">
+        <f>IF(AND($H44="",$I44=""),"",N($H44)+N($I44))</f>
+        <v/>
+      </c>
+      <c r="K44" s="14" t="n"/>
+      <c r="L44" s="19" t="n"/>
+      <c r="M44" s="17" t="n"/>
+      <c r="N44" s="24">
+        <f>IF(OR($J44="",$M44=""),"",$J44-$M44)</f>
+        <v/>
+      </c>
+      <c r="O44" s="19" t="n"/>
+      <c r="P44" s="14" t="n"/>
+    </row>
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B44" s="13" t="n"/>
-      <c r="C44" s="14">
-        <f>IFERROR(IF($B44="","",VLOOKUP($B44,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D44" s="15" t="n"/>
-      <c r="E44" s="14">
-        <f>IFERROR(IF($D44="","",VLOOKUP($D44,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="16" t="n"/>
-      <c r="H44" s="13" t="n"/>
-      <c r="I44" s="13" t="n"/>
-      <c r="J44" s="13" t="n"/>
-      <c r="K44" s="13" t="n"/>
-      <c r="L44" s="13" t="n"/>
-      <c r="M44" s="17">
-        <f>IF(OR($H44="",$L44=""),"",$H44-$L44)</f>
-        <v/>
-      </c>
-      <c r="N44" s="16" t="n"/>
-      <c r="O44" s="13" t="n"/>
-      <c r="P44" s="16" t="n"/>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" t="inlineStr">
+      <c r="B45" s="14" t="n"/>
+      <c r="C45" s="15">
+        <f>IFERROR(IF($B45="","",VLOOKUP($B45,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D45" s="14" t="n"/>
+      <c r="E45" s="15">
+        <f>IFERROR(IF($D45="","",VLOOKUP($D45,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F45" s="14" t="n"/>
+      <c r="G45" s="16">
+        <f>IFERROR(IF($F45="","",VLOOKUP($F45,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="17" t="n"/>
+      <c r="I45" s="17" t="n"/>
+      <c r="J45" s="18">
+        <f>IF(AND($H45="",$I45=""),"",N($H45)+N($I45))</f>
+        <v/>
+      </c>
+      <c r="K45" s="14" t="n"/>
+      <c r="L45" s="19" t="n"/>
+      <c r="M45" s="17" t="n"/>
+      <c r="N45" s="20">
+        <f>IF(OR($J45="",$M45=""),"",$J45-$M45)</f>
+        <v/>
+      </c>
+      <c r="O45" s="19" t="n"/>
+      <c r="P45" s="14" t="n"/>
+    </row>
+    <row r="46" ht="19" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B45" s="13" t="n"/>
-      <c r="C45" s="14">
-        <f>IFERROR(IF($B45="","",VLOOKUP($B45,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D45" s="15" t="n"/>
-      <c r="E45" s="14">
-        <f>IFERROR(IF($D45="","",VLOOKUP($D45,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F45" s="13" t="n"/>
-      <c r="G45" s="16" t="n"/>
-      <c r="H45" s="13" t="n"/>
-      <c r="I45" s="13" t="n"/>
-      <c r="J45" s="13" t="n"/>
-      <c r="K45" s="13" t="n"/>
-      <c r="L45" s="13" t="n"/>
-      <c r="M45" s="17">
-        <f>IF(OR($H45="",$L45=""),"",$H45-$L45)</f>
-        <v/>
-      </c>
-      <c r="N45" s="16" t="n"/>
-      <c r="O45" s="13" t="n"/>
-      <c r="P45" s="16" t="n"/>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" t="inlineStr">
+      <c r="B46" s="14" t="n"/>
+      <c r="C46" s="21">
+        <f>IFERROR(IF($B46="","",VLOOKUP($B46,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D46" s="14" t="n"/>
+      <c r="E46" s="21">
+        <f>IFERROR(IF($D46="","",VLOOKUP($D46,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F46" s="14" t="n"/>
+      <c r="G46" s="22">
+        <f>IFERROR(IF($F46="","",VLOOKUP($F46,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="17" t="n"/>
+      <c r="I46" s="17" t="n"/>
+      <c r="J46" s="23">
+        <f>IF(AND($H46="",$I46=""),"",N($H46)+N($I46))</f>
+        <v/>
+      </c>
+      <c r="K46" s="14" t="n"/>
+      <c r="L46" s="19" t="n"/>
+      <c r="M46" s="17" t="n"/>
+      <c r="N46" s="24">
+        <f>IF(OR($J46="",$M46=""),"",$J46-$M46)</f>
+        <v/>
+      </c>
+      <c r="O46" s="19" t="n"/>
+      <c r="P46" s="14" t="n"/>
+    </row>
+    <row r="47" ht="19" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B46" s="13" t="n"/>
-      <c r="C46" s="14">
-        <f>IFERROR(IF($B46="","",VLOOKUP($B46,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D46" s="15" t="n"/>
-      <c r="E46" s="14">
-        <f>IFERROR(IF($D46="","",VLOOKUP($D46,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F46" s="13" t="n"/>
-      <c r="G46" s="16" t="n"/>
-      <c r="H46" s="13" t="n"/>
-      <c r="I46" s="13" t="n"/>
-      <c r="J46" s="13" t="n"/>
-      <c r="K46" s="13" t="n"/>
-      <c r="L46" s="13" t="n"/>
-      <c r="M46" s="17">
-        <f>IF(OR($H46="",$L46=""),"",$H46-$L46)</f>
-        <v/>
-      </c>
-      <c r="N46" s="16" t="n"/>
-      <c r="O46" s="13" t="n"/>
-      <c r="P46" s="16" t="n"/>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" t="inlineStr">
+      <c r="B47" s="14" t="n"/>
+      <c r="C47" s="15">
+        <f>IFERROR(IF($B47="","",VLOOKUP($B47,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D47" s="14" t="n"/>
+      <c r="E47" s="15">
+        <f>IFERROR(IF($D47="","",VLOOKUP($D47,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F47" s="14" t="n"/>
+      <c r="G47" s="16">
+        <f>IFERROR(IF($F47="","",VLOOKUP($F47,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="17" t="n"/>
+      <c r="I47" s="17" t="n"/>
+      <c r="J47" s="18">
+        <f>IF(AND($H47="",$I47=""),"",N($H47)+N($I47))</f>
+        <v/>
+      </c>
+      <c r="K47" s="14" t="n"/>
+      <c r="L47" s="19" t="n"/>
+      <c r="M47" s="17" t="n"/>
+      <c r="N47" s="20">
+        <f>IF(OR($J47="",$M47=""),"",$J47-$M47)</f>
+        <v/>
+      </c>
+      <c r="O47" s="19" t="n"/>
+      <c r="P47" s="14" t="n"/>
+    </row>
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B47" s="13" t="n"/>
-      <c r="C47" s="14">
-        <f>IFERROR(IF($B47="","",VLOOKUP($B47,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D47" s="15" t="n"/>
-      <c r="E47" s="14">
-        <f>IFERROR(IF($D47="","",VLOOKUP($D47,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F47" s="13" t="n"/>
-      <c r="G47" s="16" t="n"/>
-      <c r="H47" s="13" t="n"/>
-      <c r="I47" s="13" t="n"/>
-      <c r="J47" s="13" t="n"/>
-      <c r="K47" s="13" t="n"/>
-      <c r="L47" s="13" t="n"/>
-      <c r="M47" s="17">
-        <f>IF(OR($H47="",$L47=""),"",$H47-$L47)</f>
-        <v/>
-      </c>
-      <c r="N47" s="16" t="n"/>
-      <c r="O47" s="13" t="n"/>
-      <c r="P47" s="16" t="n"/>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" t="inlineStr">
+      <c r="B48" s="14" t="n"/>
+      <c r="C48" s="21">
+        <f>IFERROR(IF($B48="","",VLOOKUP($B48,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D48" s="14" t="n"/>
+      <c r="E48" s="21">
+        <f>IFERROR(IF($D48="","",VLOOKUP($D48,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F48" s="14" t="n"/>
+      <c r="G48" s="22">
+        <f>IFERROR(IF($F48="","",VLOOKUP($F48,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="17" t="n"/>
+      <c r="I48" s="17" t="n"/>
+      <c r="J48" s="23">
+        <f>IF(AND($H48="",$I48=""),"",N($H48)+N($I48))</f>
+        <v/>
+      </c>
+      <c r="K48" s="14" t="n"/>
+      <c r="L48" s="19" t="n"/>
+      <c r="M48" s="17" t="n"/>
+      <c r="N48" s="24">
+        <f>IF(OR($J48="",$M48=""),"",$J48-$M48)</f>
+        <v/>
+      </c>
+      <c r="O48" s="19" t="n"/>
+      <c r="P48" s="14" t="n"/>
+    </row>
+    <row r="49" ht="19" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B48" s="13" t="n"/>
-      <c r="C48" s="14">
-        <f>IFERROR(IF($B48="","",VLOOKUP($B48,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D48" s="15" t="n"/>
-      <c r="E48" s="14">
-        <f>IFERROR(IF($D48="","",VLOOKUP($D48,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F48" s="13" t="n"/>
-      <c r="G48" s="16" t="n"/>
-      <c r="H48" s="13" t="n"/>
-      <c r="I48" s="13" t="n"/>
-      <c r="J48" s="13" t="n"/>
-      <c r="K48" s="13" t="n"/>
-      <c r="L48" s="13" t="n"/>
-      <c r="M48" s="17">
-        <f>IF(OR($H48="",$L48=""),"",$H48-$L48)</f>
-        <v/>
-      </c>
-      <c r="N48" s="16" t="n"/>
-      <c r="O48" s="13" t="n"/>
-      <c r="P48" s="16" t="n"/>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" t="inlineStr">
+      <c r="B49" s="14" t="n"/>
+      <c r="C49" s="15">
+        <f>IFERROR(IF($B49="","",VLOOKUP($B49,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D49" s="14" t="n"/>
+      <c r="E49" s="15">
+        <f>IFERROR(IF($D49="","",VLOOKUP($D49,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F49" s="14" t="n"/>
+      <c r="G49" s="16">
+        <f>IFERROR(IF($F49="","",VLOOKUP($F49,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="17" t="n"/>
+      <c r="I49" s="17" t="n"/>
+      <c r="J49" s="18">
+        <f>IF(AND($H49="",$I49=""),"",N($H49)+N($I49))</f>
+        <v/>
+      </c>
+      <c r="K49" s="14" t="n"/>
+      <c r="L49" s="19" t="n"/>
+      <c r="M49" s="17" t="n"/>
+      <c r="N49" s="20">
+        <f>IF(OR($J49="",$M49=""),"",$J49-$M49)</f>
+        <v/>
+      </c>
+      <c r="O49" s="19" t="n"/>
+      <c r="P49" s="14" t="n"/>
+    </row>
+    <row r="50" ht="19" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B49" s="13" t="n"/>
-      <c r="C49" s="14">
-        <f>IFERROR(IF($B49="","",VLOOKUP($B49,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D49" s="15" t="n"/>
-      <c r="E49" s="14">
-        <f>IFERROR(IF($D49="","",VLOOKUP($D49,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F49" s="13" t="n"/>
-      <c r="G49" s="16" t="n"/>
-      <c r="H49" s="13" t="n"/>
-      <c r="I49" s="13" t="n"/>
-      <c r="J49" s="13" t="n"/>
-      <c r="K49" s="13" t="n"/>
-      <c r="L49" s="13" t="n"/>
-      <c r="M49" s="17">
-        <f>IF(OR($H49="",$L49=""),"",$H49-$L49)</f>
-        <v/>
-      </c>
-      <c r="N49" s="16" t="n"/>
-      <c r="O49" s="13" t="n"/>
-      <c r="P49" s="16" t="n"/>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" t="inlineStr">
+      <c r="B50" s="14" t="n"/>
+      <c r="C50" s="21">
+        <f>IFERROR(IF($B50="","",VLOOKUP($B50,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D50" s="14" t="n"/>
+      <c r="E50" s="21">
+        <f>IFERROR(IF($D50="","",VLOOKUP($D50,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F50" s="14" t="n"/>
+      <c r="G50" s="22">
+        <f>IFERROR(IF($F50="","",VLOOKUP($F50,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="17" t="n"/>
+      <c r="I50" s="17" t="n"/>
+      <c r="J50" s="23">
+        <f>IF(AND($H50="",$I50=""),"",N($H50)+N($I50))</f>
+        <v/>
+      </c>
+      <c r="K50" s="14" t="n"/>
+      <c r="L50" s="19" t="n"/>
+      <c r="M50" s="17" t="n"/>
+      <c r="N50" s="24">
+        <f>IF(OR($J50="",$M50=""),"",$J50-$M50)</f>
+        <v/>
+      </c>
+      <c r="O50" s="19" t="n"/>
+      <c r="P50" s="14" t="n"/>
+    </row>
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B50" s="13" t="n"/>
-      <c r="C50" s="14">
-        <f>IFERROR(IF($B50="","",VLOOKUP($B50,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D50" s="15" t="n"/>
-      <c r="E50" s="14">
-        <f>IFERROR(IF($D50="","",VLOOKUP($D50,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F50" s="13" t="n"/>
-      <c r="G50" s="16" t="n"/>
-      <c r="H50" s="13" t="n"/>
-      <c r="I50" s="13" t="n"/>
-      <c r="J50" s="13" t="n"/>
-      <c r="K50" s="13" t="n"/>
-      <c r="L50" s="13" t="n"/>
-      <c r="M50" s="17">
-        <f>IF(OR($H50="",$L50=""),"",$H50-$L50)</f>
-        <v/>
-      </c>
-      <c r="N50" s="16" t="n"/>
-      <c r="O50" s="13" t="n"/>
-      <c r="P50" s="16" t="n"/>
-    </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" t="inlineStr">
+      <c r="B51" s="14" t="n"/>
+      <c r="C51" s="15">
+        <f>IFERROR(IF($B51="","",VLOOKUP($B51,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D51" s="14" t="n"/>
+      <c r="E51" s="15">
+        <f>IFERROR(IF($D51="","",VLOOKUP($D51,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F51" s="14" t="n"/>
+      <c r="G51" s="16">
+        <f>IFERROR(IF($F51="","",VLOOKUP($F51,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="17" t="n"/>
+      <c r="I51" s="17" t="n"/>
+      <c r="J51" s="18">
+        <f>IF(AND($H51="",$I51=""),"",N($H51)+N($I51))</f>
+        <v/>
+      </c>
+      <c r="K51" s="14" t="n"/>
+      <c r="L51" s="19" t="n"/>
+      <c r="M51" s="17" t="n"/>
+      <c r="N51" s="20">
+        <f>IF(OR($J51="",$M51=""),"",$J51-$M51)</f>
+        <v/>
+      </c>
+      <c r="O51" s="19" t="n"/>
+      <c r="P51" s="14" t="n"/>
+    </row>
+    <row r="52" ht="19" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B51" s="13" t="n"/>
-      <c r="C51" s="14">
-        <f>IFERROR(IF($B51="","",VLOOKUP($B51,EmpTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="D51" s="15" t="n"/>
-      <c r="E51" s="14">
-        <f>IFERROR(IF($D51="","",VLOOKUP($D51,TradeTable,2,FALSE)),"?")</f>
-        <v/>
-      </c>
-      <c r="F51" s="13" t="n"/>
-      <c r="G51" s="16" t="n"/>
-      <c r="H51" s="13" t="n"/>
-      <c r="I51" s="13" t="n"/>
-      <c r="J51" s="13" t="n"/>
-      <c r="K51" s="13" t="n"/>
-      <c r="L51" s="13" t="n"/>
-      <c r="M51" s="17">
-        <f>IF(OR($H51="",$L51=""),"",$H51-$L51)</f>
-        <v/>
-      </c>
-      <c r="N51" s="16" t="n"/>
-      <c r="O51" s="13" t="n"/>
-      <c r="P51" s="16" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B52" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="H52" s="19">
-        <f>SUM(H12:H51)</f>
-        <v/>
-      </c>
-      <c r="I52" s="19">
-        <f>SUM(I12:I51)</f>
-        <v/>
-      </c>
-      <c r="J52" s="19">
-        <f>SUM(J12:J51)</f>
-        <v/>
-      </c>
-      <c r="L52" s="19">
-        <f>SUM(L12:L51)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="20" t="inlineStr">
-        <is>
-          <t>Description of work accomplished, issues encountered, etc.</t>
-        </is>
-      </c>
+      <c r="B52" s="14" t="n"/>
+      <c r="C52" s="21">
+        <f>IFERROR(IF($B52="","",VLOOKUP($B52,EmpTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="D52" s="14" t="n"/>
+      <c r="E52" s="21">
+        <f>IFERROR(IF($D52="","",VLOOKUP($D52,TradeTable,2,FALSE)),"?")</f>
+        <v/>
+      </c>
+      <c r="F52" s="14" t="n"/>
+      <c r="G52" s="22">
+        <f>IFERROR(IF($F52="","",VLOOKUP($F52,WOTable,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="17" t="n"/>
+      <c r="I52" s="17" t="n"/>
+      <c r="J52" s="23">
+        <f>IF(AND($H52="",$I52=""),"",N($H52)+N($I52))</f>
+        <v/>
+      </c>
+      <c r="K52" s="14" t="n"/>
+      <c r="L52" s="19" t="n"/>
+      <c r="M52" s="17" t="n"/>
+      <c r="N52" s="24">
+        <f>IF(OR($J52="",$M52=""),"",$J52-$M52)</f>
+        <v/>
+      </c>
+      <c r="O52" s="19" t="n"/>
+      <c r="P52" s="14" t="n"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="B53" s="25" t="inlineStr">
+        <is>
+          <t>DAILY TOTAL</t>
+        </is>
+      </c>
+      <c r="G53" s="26" t="n"/>
+      <c r="H53" s="27">
+        <f>SUM(H13:H52)</f>
+        <v/>
+      </c>
+      <c r="I53" s="27">
+        <f>SUM(I13:I52)</f>
+        <v/>
+      </c>
+      <c r="J53" s="27">
+        <f>SUM(J13:J52)</f>
+        <v/>
+      </c>
+      <c r="K53" s="26" t="n"/>
+      <c r="L53" s="26" t="n"/>
+      <c r="M53" s="27">
+        <f>SUM(M13:M52)</f>
+        <v/>
+      </c>
+      <c r="N53" s="26" t="n"/>
+      <c r="O53" s="26" t="n"/>
+      <c r="P53" s="26" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="21" t="n"/>
-    </row>
-    <row r="56"/>
+      <c r="B55" s="28" t="inlineStr">
+        <is>
+          <t>Notes — work accomplished, issues, hold-ups</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="29" t="n"/>
+    </row>
     <row r="57"/>
     <row r="58"/>
+    <row r="59"/>
+    <row r="61">
+      <c r="B61" s="30" t="inlineStr">
+        <is>
+          <t>LEGEND:</t>
+        </is>
+      </c>
+      <c r="C61" s="31" t="n"/>
+      <c r="D61" s="32" t="inlineStr">
+        <is>
+          <t>You fill in</t>
+        </is>
+      </c>
+      <c r="F61" s="33" t="n"/>
+      <c r="G61" s="32" t="inlineStr">
+        <is>
+          <t>Auto-filled</t>
+        </is>
+      </c>
+      <c r="I61" s="34" t="n"/>
+      <c r="J61" s="32" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="L61" s="35" t="n"/>
+      <c r="M61" s="32" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="F2:M2"/>
-    <mergeCell ref="H7:M8"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="F3:M3"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="B55:P58"/>
+  <mergeCells count="29">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D3:J3"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B11:L11"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="M11:P11"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="B56:L59"/>
+    <mergeCell ref="B5:L5"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="H6:J6"/>
   </mergeCells>
-  <conditionalFormatting sqref="B12:B51">
+  <conditionalFormatting sqref="B13:B52">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND($B12&lt;&gt;"",$C12="?")</formula>
+      <formula>AND($B13&lt;&gt;"",$C13="?")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D12:D51">
+  <conditionalFormatting sqref="D13:D52">
     <cfRule type="expression" priority="2" dxfId="0">
-      <formula>AND($D12&lt;&gt;"",$E12="?")</formula>
+      <formula>AND($D13&lt;&gt;"",$E13="?")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M12:M51">
+  <conditionalFormatting sqref="N13:N52">
     <cfRule type="expression" priority="3" dxfId="0">
-      <formula>AND($M12&lt;&gt;"",$M12&lt;&gt;0)</formula>
+      <formula>AND($N13&lt;&gt;"",$N13&lt;&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12:H51">
+  <conditionalFormatting sqref="J13:J52">
     <cfRule type="expression" priority="4" dxfId="0">
-      <formula>OR($H12&gt;16,$H12&lt;0)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="1">
-      <formula>AND($H12&lt;&gt;"",$I12+$J12&lt;&gt;$H12)</formula>
+      <formula>OR($J13&gt;16,$J13&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
-    <dataValidation sqref="B12:B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=ShiftList</formula1>
+    </dataValidation>
+    <dataValidation sqref="B13:B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=EmpNames</formula1>
     </dataValidation>
-    <dataValidation sqref="D12:D51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D13:D52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=TradeNames</formula1>
     </dataValidation>
-    <dataValidation sqref="F12:F51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=WOList</formula1>
+    <dataValidation sqref="F13:F52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=WONames</formula1>
     </dataValidation>
-    <dataValidation sqref="K12:K51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K13:K52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LocList</formula1>
     </dataValidation>
-    <dataValidation sqref="N12:N51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O13:O52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=SwipeList</formula1>
     </dataValidation>
-    <dataValidation sqref="O12:O51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P13:P52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=HoldUpList</formula1>
-    </dataValidation>
-    <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=ShiftList</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2247,7 +2662,7 @@
   <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
@@ -2261,361 +2676,361 @@
     <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="22" t="inlineStr">
-        <is>
-          <t>EMPLOYEES  (add new people here — dropdowns update automatically)</t>
-        </is>
-      </c>
-      <c r="F1" s="22" t="inlineStr">
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>EMPLOYEES   (add people here — dropdowns update automatically)</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>TRADES  -&gt;  SAP ACTIVITY TYPE</t>
         </is>
       </c>
-      <c r="K1" s="22" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>PICK LISTS</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="36" t="inlineStr">
         <is>
           <t>Employee Name</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="36" t="inlineStr">
         <is>
           <t>CF ID</t>
         </is>
       </c>
-      <c r="C2" s="23" t="inlineStr">
+      <c r="C2" s="36" t="inlineStr">
         <is>
           <t>Default Work Center</t>
         </is>
       </c>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="D2" s="36" t="inlineStr">
         <is>
           <t>Default Trade</t>
         </is>
       </c>
-      <c r="F2" s="23" t="inlineStr">
+      <c r="F2" s="36" t="inlineStr">
         <is>
           <t>Trade / Position</t>
         </is>
       </c>
-      <c r="G2" s="23" t="inlineStr">
+      <c r="G2" s="36" t="inlineStr">
         <is>
           <t>Activity Type</t>
         </is>
       </c>
-      <c r="H2" s="23" t="inlineStr">
+      <c r="H2" s="36" t="inlineStr">
         <is>
           <t>Activity Type Description</t>
         </is>
       </c>
-      <c r="I2" s="23" t="inlineStr">
+      <c r="I2" s="36" t="inlineStr">
         <is>
           <t>Work Center</t>
         </is>
       </c>
-      <c r="K2" s="23" t="inlineStr">
+      <c r="K2" s="36" t="inlineStr">
         <is>
           <t>Shift</t>
         </is>
       </c>
-      <c r="L2" s="23" t="inlineStr">
+      <c r="L2" s="36" t="inlineStr">
         <is>
           <t>Work Location</t>
         </is>
       </c>
-      <c r="M2" s="23" t="inlineStr">
+      <c r="M2" s="36" t="inlineStr">
         <is>
           <t>Swipe Deviation</t>
         </is>
       </c>
-      <c r="N2" s="23" t="inlineStr">
+      <c r="N2" s="36" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="37" t="inlineStr">
         <is>
           <t>Winter, Tom</t>
         </is>
       </c>
-      <c r="B3" s="24" t="n">
+      <c r="B3" s="37" t="n">
         <v>19057</v>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="37" t="inlineStr">
         <is>
           <t>PF01</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
+      <c r="D3" s="37" t="inlineStr">
         <is>
           <t>Pipefitter - Foreman</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pipefitter - Foreman</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="37" t="inlineStr">
         <is>
           <t>CI201</t>
         </is>
       </c>
-      <c r="H3" s="24" t="inlineStr">
+      <c r="H3" s="37" t="inlineStr">
         <is>
           <t>CRT CIM PF FM ST</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="37" t="inlineStr">
         <is>
           <t>PF01</t>
         </is>
       </c>
-      <c r="K3" s="24" t="inlineStr">
+      <c r="K3" s="37" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="L3" s="24" t="inlineStr">
+      <c r="L3" s="37" t="inlineStr">
         <is>
           <t>1 - Shop Floor</t>
         </is>
       </c>
-      <c r="M3" s="24" t="inlineStr">
+      <c r="M3" s="37" t="inlineStr">
         <is>
           <t>Call In</t>
         </is>
       </c>
-      <c r="N3" s="24" t="inlineStr">
+      <c r="N3" s="37" t="inlineStr">
         <is>
           <t>Approved Offsite / Swipe Deviation</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>Power, Nathan</t>
         </is>
       </c>
-      <c r="B4" s="24" t="n">
+      <c r="B4" s="37" t="n">
         <v>19058</v>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="37" t="inlineStr">
         <is>
           <t>PF01</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>Pipefitter - Journeyman</t>
         </is>
       </c>
-      <c r="F4" s="24" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pipefitter - Foreman (DT)</t>
         </is>
       </c>
-      <c r="G4" s="24" t="inlineStr">
+      <c r="G4" s="37" t="inlineStr">
         <is>
           <t>CI202</t>
         </is>
       </c>
-      <c r="H4" s="24" t="inlineStr">
+      <c r="H4" s="37" t="inlineStr">
         <is>
           <t>CRT CIM PF FM DT</t>
         </is>
       </c>
-      <c r="I4" s="24" t="inlineStr">
+      <c r="I4" s="37" t="inlineStr">
         <is>
           <t>PF01</t>
         </is>
       </c>
-      <c r="K4" s="24" t="inlineStr">
+      <c r="K4" s="37" t="inlineStr">
         <is>
           <t>Night</t>
         </is>
       </c>
-      <c r="L4" s="24" t="inlineStr">
+      <c r="L4" s="37" t="inlineStr">
         <is>
           <t>2 - Office</t>
         </is>
       </c>
-      <c r="M4" s="24" t="inlineStr">
+      <c r="M4" s="37" t="inlineStr">
         <is>
           <t>Remote Work / Offsite Meeting</t>
         </is>
       </c>
-      <c r="N4" s="24" t="inlineStr">
+      <c r="N4" s="37" t="inlineStr">
         <is>
           <t>Decision Needed to Proceed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Vellinga, Rob</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="37" t="n">
         <v>19059</v>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>PF01</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>Pipefitter - Journeyman</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pipefitter - Journeyman</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="37" t="inlineStr">
         <is>
           <t>CI203</t>
         </is>
       </c>
-      <c r="H5" s="24" t="inlineStr">
+      <c r="H5" s="37" t="inlineStr">
         <is>
           <t>CRT CIM PF JM ST</t>
         </is>
       </c>
-      <c r="I5" s="24" t="inlineStr">
+      <c r="I5" s="37" t="inlineStr">
         <is>
           <t>PF01</t>
         </is>
       </c>
-      <c r="L5" s="24" t="inlineStr">
+      <c r="L5" s="37" t="inlineStr">
         <is>
           <t>3 - Field</t>
         </is>
       </c>
-      <c r="M5" s="24" t="inlineStr">
+      <c r="M5" s="37" t="inlineStr">
         <is>
           <t>Safety - Fit for Duty Checks</t>
         </is>
       </c>
-      <c r="N5" s="24" t="inlineStr">
+      <c r="N5" s="37" t="inlineStr">
         <is>
           <t>Equip Avail, Not Prepped</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>Carter, Brad</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="37" t="n">
         <v>19060</v>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>PF01</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>Pipefitter - Journeyman</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Pipefitter - Journeyman (DT)</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="37" t="inlineStr">
         <is>
           <t>CI204</t>
         </is>
       </c>
-      <c r="H6" s="24" t="inlineStr">
+      <c r="H6" s="37" t="inlineStr">
         <is>
           <t>CRT CIM PF JM DT</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr">
+      <c r="I6" s="37" t="inlineStr">
         <is>
           <t>PF01</t>
         </is>
       </c>
-      <c r="M6" s="24" t="inlineStr">
+      <c r="M6" s="37" t="inlineStr">
         <is>
           <t>Shop Fabrication</t>
         </is>
       </c>
-      <c r="N6" s="24" t="inlineStr">
+      <c r="N6" s="37" t="inlineStr">
         <is>
           <t>Equip Not Avail</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>Wright, Corey</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="37" t="n">
         <v>19061</v>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>PF01</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>Pipefitter - Journeyman</t>
         </is>
       </c>
-      <c r="M7" s="24" t="inlineStr">
+      <c r="M7" s="37" t="inlineStr">
         <is>
           <t>Shop Visit / Materials Pickup</t>
         </is>
       </c>
-      <c r="N7" s="24" t="inlineStr">
+      <c r="N7" s="37" t="inlineStr">
         <is>
           <t>Parts/Material Not Avail</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="M8" s="24" t="inlineStr">
+      <c r="M8" s="37" t="inlineStr">
         <is>
           <t>Show Up Time</t>
         </is>
       </c>
-      <c r="N8" s="24" t="inlineStr">
+      <c r="N8" s="37" t="inlineStr">
         <is>
           <t>Permit Delay</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="N9" s="24" t="inlineStr">
+      <c r="N9" s="37" t="inlineStr">
         <is>
           <t>Prev Op Not Complete</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="N10" s="24" t="inlineStr">
+      <c r="N10" s="37" t="inlineStr">
         <is>
           <t>Priority Change by Owner</t>
         </is>
@@ -2667,1580 +3082,1580 @@
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="22" t="inlineStr">
-        <is>
-          <t>SAP WORK ORDERS  (from IW29 export — refresh each day)</t>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>SAP WORK ORDERS   (from IW29 — refresh daily)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="36" t="inlineStr">
         <is>
           <t>Work Order</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="36" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C2" s="23" t="inlineStr">
+      <c r="C2" s="36" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="D2" s="36" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="37" t="inlineStr">
         <is>
           <t>40026808</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="37" t="inlineStr">
         <is>
           <t>TA-J402-Major</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D3" s="24" t="inlineStr">
+      <c r="C3" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D3" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>40030041</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>TA-JM104-Overhaul</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="C4" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>60015157</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>TA-Relocate 5kV Feeder Cables</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>ELE1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>60015158</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>TA-T22 Increase Tap Changer</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>ELE1</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>60015159</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>TA-C/T Increase Tap Changer</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>ELE1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>60015200</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>TA-401 Increase Tap Changer</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>ELE1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>60015201</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>TA-Rplce HONI Poles on M2 and M8 feeders</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>ELE1</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>60015202</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>TA-Remove Unused Circuits from Sub 2</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
         <is>
           <t>ELE1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>60015203</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>TA-Remove Unused Circuits from Sub 3</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D11" s="37" t="inlineStr">
         <is>
           <t>ELE1</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>60015204</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>TA-G605B-Replace Discharge Block Valve</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D12" s="37" t="inlineStr">
         <is>
           <t>OFS1</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>60015205</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>TA-3CM109-Visual Inspection</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>TA70019</t>
         </is>
       </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>NA01</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>60015206</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>TA-G105-Replace Coarse and Fine Filters</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>60015207</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>TA-OLLR Repair-8FV4140 Bypass Line</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="37" t="inlineStr">
         <is>
           <t>60015208</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>TA-D102-Open for Catalyst Change</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="37" t="inlineStr">
         <is>
           <t>60015212</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>TA-E404A-Desiccant Change</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D17" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="37" t="inlineStr">
         <is>
           <t>60015213</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>TA-E404B-Desiccant Change</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="C18" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D18" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>60015217</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>TA-Install A2 Master Blanks</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="C19" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D19" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="37" t="inlineStr">
         <is>
           <t>60015218</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>TA-Remove A2 Master Blanks</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="C20" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D20" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t>60015219</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>TA-Nuc Source Removals</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="37" t="inlineStr">
         <is>
           <t>TA70018</t>
         </is>
       </c>
-      <c r="D21" s="24" t="inlineStr">
+      <c r="D21" s="37" t="inlineStr">
         <is>
           <t>URM1</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="37" t="inlineStr">
         <is>
           <t>60015220</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>TA-Nuc Source Installations</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="37" t="inlineStr">
         <is>
           <t>TA70018</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="37" t="inlineStr">
         <is>
           <t>URM1</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="37" t="inlineStr">
         <is>
           <t>60015223</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>TA-OLLR Removal-ROB Near L501s</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
+      <c r="C23" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D23" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>60015225</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="37" t="inlineStr">
         <is>
           <t>TA-G401-Replace Insulation</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D24" s="24" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D24" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="37" t="inlineStr">
         <is>
           <t>60015183</t>
         </is>
       </c>
-      <c r="B25" s="24" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>TA-5XV7364-Top Removal/Overhaul</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D25" s="37" t="inlineStr">
         <is>
           <t>UTI1</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="37" t="inlineStr">
         <is>
           <t>60015184</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="37" t="inlineStr">
         <is>
           <t>TA-5XV7366-Top Removal/Overhaul</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D26" s="37" t="inlineStr">
         <is>
           <t>UTI1</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="37" t="inlineStr">
         <is>
           <t>60015260</t>
         </is>
       </c>
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B27" s="37" t="inlineStr">
         <is>
           <t>TA-E22-097-Site Ladder Upgrades</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="inlineStr">
+      <c r="C27" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D27" s="37" t="inlineStr">
         <is>
           <t>GRN1</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="37" t="inlineStr">
         <is>
           <t>20000752</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="37" t="inlineStr">
         <is>
           <t>E22-097-Site Ladder Upgrades</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D28" s="24" t="inlineStr">
+      <c r="C28" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D28" s="37" t="inlineStr">
         <is>
           <t>FAC1</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="37" t="inlineStr">
         <is>
           <t>60015343</t>
         </is>
       </c>
-      <c r="B29" s="24" t="inlineStr">
+      <c r="B29" s="37" t="inlineStr">
         <is>
           <t>TA-J810A-Nozzle,Screens &amp; Header Insp</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D29" s="24" t="inlineStr"/>
+      <c r="C29" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D29" s="37" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="37" t="inlineStr">
         <is>
           <t>60015344</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="37" t="inlineStr">
         <is>
           <t>TA-J810B-Nozzle,Screens &amp; Header Insp</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D30" s="24" t="inlineStr">
+      <c r="C30" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D30" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="37" t="inlineStr">
         <is>
           <t>60015345</t>
         </is>
       </c>
-      <c r="B31" s="24" t="inlineStr">
+      <c r="B31" s="37" t="inlineStr">
         <is>
           <t>TA-J810C-Nozzle,Screens &amp; Header Insp</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D31" s="24" t="inlineStr">
+      <c r="C31" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D31" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="37" t="inlineStr">
         <is>
           <t>60015350</t>
         </is>
       </c>
-      <c r="B32" s="24" t="inlineStr">
+      <c r="B32" s="37" t="inlineStr">
         <is>
           <t>TA-T1 Sight Glass Replace/Eliminate</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C32" s="37" t="inlineStr">
         <is>
           <t>TA70018</t>
         </is>
       </c>
-      <c r="D32" s="24" t="inlineStr">
+      <c r="D32" s="37" t="inlineStr">
         <is>
           <t>URM1</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="24" t="inlineStr">
+      <c r="A33" s="37" t="inlineStr">
         <is>
           <t>60015351</t>
         </is>
       </c>
-      <c r="B33" s="24" t="inlineStr">
+      <c r="B33" s="37" t="inlineStr">
         <is>
           <t>TA-E121 Sight Glass Replace/Eliminate</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="37" t="inlineStr">
         <is>
           <t>TA70018</t>
         </is>
       </c>
-      <c r="D33" s="24" t="inlineStr">
+      <c r="D33" s="37" t="inlineStr">
         <is>
           <t>URM1</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="37" t="inlineStr">
         <is>
           <t>60015352</t>
         </is>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B34" s="37" t="inlineStr">
         <is>
           <t>TA-E122 Sight Glass Replace/Eliminate</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="37" t="inlineStr">
         <is>
           <t>TA70018</t>
         </is>
       </c>
-      <c r="D34" s="24" t="inlineStr">
+      <c r="D34" s="37" t="inlineStr">
         <is>
           <t>URM1</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24" t="inlineStr">
+      <c r="A35" s="37" t="inlineStr">
         <is>
           <t>60015353</t>
         </is>
       </c>
-      <c r="B35" s="24" t="inlineStr">
+      <c r="B35" s="37" t="inlineStr">
         <is>
           <t>TA-E123 Sight Glass Replace/Eliminate</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C35" s="37" t="inlineStr">
         <is>
           <t>TA70018</t>
         </is>
       </c>
-      <c r="D35" s="24" t="inlineStr">
+      <c r="D35" s="37" t="inlineStr">
         <is>
           <t>URM1</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="24" t="inlineStr">
+      <c r="A36" s="37" t="inlineStr">
         <is>
           <t>40031322</t>
         </is>
       </c>
-      <c r="B36" s="24" t="inlineStr">
+      <c r="B36" s="37" t="inlineStr">
         <is>
           <t>TA-D120-Replace Sight Glass with New</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C36" s="37" t="inlineStr">
         <is>
           <t>TA70018</t>
         </is>
       </c>
-      <c r="D36" s="24" t="inlineStr">
+      <c r="D36" s="37" t="inlineStr">
         <is>
           <t>URM1</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="24" t="inlineStr">
+      <c r="A37" s="37" t="inlineStr">
         <is>
           <t>40031323</t>
         </is>
       </c>
-      <c r="B37" s="24" t="inlineStr">
+      <c r="B37" s="37" t="inlineStr">
         <is>
           <t>TA-D121-Replace Sight Glass with New</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C37" s="37" t="inlineStr">
         <is>
           <t>TA70018</t>
         </is>
       </c>
-      <c r="D37" s="24" t="inlineStr">
+      <c r="D37" s="37" t="inlineStr">
         <is>
           <t>URM1</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24" t="inlineStr">
+      <c r="A38" s="37" t="inlineStr">
         <is>
           <t>80000382</t>
         </is>
       </c>
-      <c r="B38" s="24" t="inlineStr">
+      <c r="B38" s="37" t="inlineStr">
         <is>
           <t>TA 2026 - Indirect Blast Resistant Trail</t>
         </is>
       </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D38" s="24" t="inlineStr">
+      <c r="C38" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D38" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="24" t="inlineStr">
+      <c r="A39" s="37" t="inlineStr">
         <is>
           <t>80000383</t>
         </is>
       </c>
-      <c r="B39" s="24" t="inlineStr">
+      <c r="B39" s="37" t="inlineStr">
         <is>
           <t>TA 2026 - Indirect Blast Resistant Trail</t>
         </is>
       </c>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="C39" s="37" t="inlineStr">
         <is>
           <t>TA70019</t>
         </is>
       </c>
-      <c r="D39" s="24" t="inlineStr">
+      <c r="D39" s="37" t="inlineStr">
         <is>
           <t>NA01</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="inlineStr">
+      <c r="A40" s="37" t="inlineStr">
         <is>
           <t>80000384</t>
         </is>
       </c>
-      <c r="B40" s="24" t="inlineStr">
+      <c r="B40" s="37" t="inlineStr">
         <is>
           <t>TA 2026 - Indirect Blast Resistant Trail</t>
         </is>
       </c>
-      <c r="C40" s="24" t="inlineStr">
+      <c r="C40" s="37" t="inlineStr">
         <is>
           <t>TA70018</t>
         </is>
       </c>
-      <c r="D40" s="24" t="inlineStr">
+      <c r="D40" s="37" t="inlineStr">
         <is>
           <t>URM1</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="24" t="inlineStr">
+      <c r="A41" s="37" t="inlineStr">
         <is>
           <t>80000385</t>
         </is>
       </c>
-      <c r="B41" s="24" t="inlineStr">
+      <c r="B41" s="37" t="inlineStr">
         <is>
           <t>TA 2026 - Rental Equipment for NA</t>
         </is>
       </c>
-      <c r="C41" s="24" t="inlineStr">
+      <c r="C41" s="37" t="inlineStr">
         <is>
           <t>TA70019</t>
         </is>
       </c>
-      <c r="D41" s="24" t="inlineStr">
+      <c r="D41" s="37" t="inlineStr">
         <is>
           <t>NA01</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="37" t="inlineStr">
         <is>
           <t>60029962</t>
         </is>
       </c>
-      <c r="B42" s="24" t="inlineStr">
+      <c r="B42" s="37" t="inlineStr">
         <is>
           <t>TA-8PV3095-Overhaul</t>
         </is>
       </c>
-      <c r="C42" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D42" s="24" t="inlineStr">
+      <c r="C42" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D42" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="24" t="inlineStr">
+      <c r="A43" s="37" t="inlineStr">
         <is>
           <t>60029964</t>
         </is>
       </c>
-      <c r="B43" s="24" t="inlineStr">
+      <c r="B43" s="37" t="inlineStr">
         <is>
           <t>TA-8PV4150-Overhaul</t>
         </is>
       </c>
-      <c r="C43" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D43" s="24" t="inlineStr">
+      <c r="C43" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D43" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="24" t="inlineStr">
+      <c r="A44" s="37" t="inlineStr">
         <is>
           <t>60029965</t>
         </is>
       </c>
-      <c r="B44" s="24" t="inlineStr">
+      <c r="B44" s="37" t="inlineStr">
         <is>
           <t>TA-C/T A Cell Isolation Repair/Replace</t>
         </is>
       </c>
-      <c r="C44" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D44" s="24" t="inlineStr">
+      <c r="C44" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D44" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="24" t="inlineStr">
+      <c r="A45" s="37" t="inlineStr">
         <is>
           <t>60029967</t>
         </is>
       </c>
-      <c r="B45" s="24" t="inlineStr">
+      <c r="B45" s="37" t="inlineStr">
         <is>
           <t>TA-C/T B Cell Isolation Repair/Replace</t>
         </is>
       </c>
-      <c r="C45" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D45" s="24" t="inlineStr">
+      <c r="C45" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D45" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="24" t="inlineStr">
+      <c r="A46" s="37" t="inlineStr">
         <is>
           <t>60029968</t>
         </is>
       </c>
-      <c r="B46" s="24" t="inlineStr">
+      <c r="B46" s="37" t="inlineStr">
         <is>
           <t>TA-C/T C Cell Isolation Repair/Replace</t>
         </is>
       </c>
-      <c r="C46" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D46" s="24" t="inlineStr">
+      <c r="C46" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D46" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="24" t="inlineStr">
+      <c r="A47" s="37" t="inlineStr">
         <is>
           <t>60029988</t>
         </is>
       </c>
-      <c r="B47" s="24" t="inlineStr">
+      <c r="B47" s="37" t="inlineStr">
         <is>
           <t>TA - Grinnel Valve overhauls</t>
         </is>
       </c>
-      <c r="C47" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D47" s="24" t="inlineStr">
+      <c r="C47" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D47" s="37" t="inlineStr">
         <is>
           <t>UTI1</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="24" t="inlineStr">
+      <c r="A48" s="37" t="inlineStr">
         <is>
           <t>60030326</t>
         </is>
       </c>
-      <c r="B48" s="24" t="inlineStr">
+      <c r="B48" s="37" t="inlineStr">
         <is>
           <t>Install Urea Master Blanks</t>
         </is>
       </c>
-      <c r="C48" s="24" t="inlineStr">
+      <c r="C48" s="37" t="inlineStr">
         <is>
           <t>TA70018</t>
         </is>
       </c>
-      <c r="D48" s="24" t="inlineStr">
+      <c r="D48" s="37" t="inlineStr">
         <is>
           <t>URM1</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="24" t="inlineStr">
+      <c r="A49" s="37" t="inlineStr">
         <is>
           <t>60030327</t>
         </is>
       </c>
-      <c r="B49" s="24" t="inlineStr">
+      <c r="B49" s="37" t="inlineStr">
         <is>
           <t>Remove Urea Master Blanks</t>
         </is>
       </c>
-      <c r="C49" s="24" t="inlineStr">
+      <c r="C49" s="37" t="inlineStr">
         <is>
           <t>TA70018</t>
         </is>
       </c>
-      <c r="D49" s="24" t="inlineStr">
+      <c r="D49" s="37" t="inlineStr">
         <is>
           <t>URM1</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="24" t="inlineStr">
+      <c r="A50" s="37" t="inlineStr">
         <is>
           <t>60030328</t>
         </is>
       </c>
-      <c r="B50" s="24" t="inlineStr">
+      <c r="B50" s="37" t="inlineStr">
         <is>
           <t>Install Nitric Acid Master Blanks</t>
         </is>
       </c>
-      <c r="C50" s="24" t="inlineStr">
+      <c r="C50" s="37" t="inlineStr">
         <is>
           <t>TA70019</t>
         </is>
       </c>
-      <c r="D50" s="24" t="inlineStr">
+      <c r="D50" s="37" t="inlineStr">
         <is>
           <t>NA01</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="24" t="inlineStr">
+      <c r="A51" s="37" t="inlineStr">
         <is>
           <t>60030330</t>
         </is>
       </c>
-      <c r="B51" s="24" t="inlineStr">
+      <c r="B51" s="37" t="inlineStr">
         <is>
           <t>Remove Nitric Acid Master Blanks</t>
         </is>
       </c>
-      <c r="C51" s="24" t="inlineStr">
+      <c r="C51" s="37" t="inlineStr">
         <is>
           <t>TA70019</t>
         </is>
       </c>
-      <c r="D51" s="24" t="inlineStr">
+      <c r="D51" s="37" t="inlineStr">
         <is>
           <t>NA01</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="24" t="inlineStr">
+      <c r="A52" s="37" t="inlineStr">
         <is>
           <t>60039047</t>
         </is>
       </c>
-      <c r="B52" s="24" t="inlineStr">
+      <c r="B52" s="37" t="inlineStr">
         <is>
           <t>A2 and Distribution PSV Overhauls</t>
         </is>
       </c>
-      <c r="C52" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D52" s="24" t="inlineStr">
+      <c r="C52" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D52" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="24" t="inlineStr">
+      <c r="A53" s="37" t="inlineStr">
         <is>
           <t>60039048</t>
         </is>
       </c>
-      <c r="B53" s="24" t="inlineStr">
+      <c r="B53" s="37" t="inlineStr">
         <is>
           <t>Urea PSV Overhauls</t>
         </is>
       </c>
-      <c r="C53" s="24" t="inlineStr">
+      <c r="C53" s="37" t="inlineStr">
         <is>
           <t>TA70018</t>
         </is>
       </c>
-      <c r="D53" s="24" t="inlineStr"/>
+      <c r="D53" s="37" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="24" t="inlineStr">
+      <c r="A54" s="37" t="inlineStr">
         <is>
           <t>60039050</t>
         </is>
       </c>
-      <c r="B54" s="24" t="inlineStr">
+      <c r="B54" s="37" t="inlineStr">
         <is>
           <t>Nitric Acid PSV Overhauls</t>
         </is>
       </c>
-      <c r="C54" s="24" t="inlineStr">
+      <c r="C54" s="37" t="inlineStr">
         <is>
           <t>TA70019</t>
         </is>
       </c>
-      <c r="D54" s="24" t="inlineStr"/>
+      <c r="D54" s="37" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="24" t="inlineStr">
+      <c r="A55" s="37" t="inlineStr">
         <is>
           <t>60039266</t>
         </is>
       </c>
-      <c r="B55" s="24" t="inlineStr">
+      <c r="B55" s="37" t="inlineStr">
         <is>
           <t>TA–8PSV1906–Overhaul</t>
         </is>
       </c>
-      <c r="C55" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D55" s="24" t="inlineStr">
+      <c r="C55" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D55" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="24" t="inlineStr">
+      <c r="A56" s="37" t="inlineStr">
         <is>
           <t>60039267</t>
         </is>
       </c>
-      <c r="B56" s="24" t="inlineStr">
+      <c r="B56" s="37" t="inlineStr">
         <is>
           <t>TA–8PSV1916A–Overhaul</t>
         </is>
       </c>
-      <c r="C56" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D56" s="24" t="inlineStr">
+      <c r="C56" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D56" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="24" t="inlineStr">
+      <c r="A57" s="37" t="inlineStr">
         <is>
           <t>60039268</t>
         </is>
       </c>
-      <c r="B57" s="24" t="inlineStr">
+      <c r="B57" s="37" t="inlineStr">
         <is>
           <t>TA–8PSV1916B–Overhaul</t>
         </is>
       </c>
-      <c r="C57" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D57" s="24" t="inlineStr">
+      <c r="C57" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D57" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="24" t="inlineStr">
+      <c r="A58" s="37" t="inlineStr">
         <is>
           <t>60039269</t>
         </is>
       </c>
-      <c r="B58" s="24" t="inlineStr">
+      <c r="B58" s="37" t="inlineStr">
         <is>
           <t>TA–8PSV1918A–Overhaul</t>
         </is>
       </c>
-      <c r="C58" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D58" s="24" t="inlineStr">
+      <c r="C58" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D58" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="24" t="inlineStr">
+      <c r="A59" s="37" t="inlineStr">
         <is>
           <t>60039270</t>
         </is>
       </c>
-      <c r="B59" s="24" t="inlineStr">
+      <c r="B59" s="37" t="inlineStr">
         <is>
           <t>TA–8PSV1918B–Overhaul</t>
         </is>
       </c>
-      <c r="C59" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D59" s="24" t="inlineStr">
+      <c r="C59" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D59" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="24" t="inlineStr">
+      <c r="A60" s="37" t="inlineStr">
         <is>
           <t>60039271</t>
         </is>
       </c>
-      <c r="B60" s="24" t="inlineStr">
+      <c r="B60" s="37" t="inlineStr">
         <is>
           <t>TA–8PSV1920A–Overhaul</t>
         </is>
       </c>
-      <c r="C60" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D60" s="24" t="inlineStr">
+      <c r="C60" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D60" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="24" t="inlineStr">
+      <c r="A61" s="37" t="inlineStr">
         <is>
           <t>60039272</t>
         </is>
       </c>
-      <c r="B61" s="24" t="inlineStr">
+      <c r="B61" s="37" t="inlineStr">
         <is>
           <t>TA–8PSV1920B–Overhaul</t>
         </is>
       </c>
-      <c r="C61" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D61" s="24" t="inlineStr">
+      <c r="C61" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D61" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="24" t="inlineStr">
+      <c r="A62" s="37" t="inlineStr">
         <is>
           <t>60039273</t>
         </is>
       </c>
-      <c r="B62" s="24" t="inlineStr">
+      <c r="B62" s="37" t="inlineStr">
         <is>
           <t>TA–8PSV1921–Overhaul</t>
         </is>
       </c>
-      <c r="C62" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D62" s="24" t="inlineStr">
+      <c r="C62" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D62" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="24" t="inlineStr">
+      <c r="A63" s="37" t="inlineStr">
         <is>
           <t>60039275</t>
         </is>
       </c>
-      <c r="B63" s="24" t="inlineStr">
+      <c r="B63" s="37" t="inlineStr">
         <is>
           <t>TA–8PSV1922–Overhaul</t>
         </is>
       </c>
-      <c r="C63" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D63" s="24" t="inlineStr">
+      <c r="C63" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D63" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="24" t="inlineStr">
+      <c r="A64" s="37" t="inlineStr">
         <is>
           <t>60039276</t>
         </is>
       </c>
-      <c r="B64" s="24" t="inlineStr">
+      <c r="B64" s="37" t="inlineStr">
         <is>
           <t>TA–8PSV1987–Overhaul</t>
         </is>
       </c>
-      <c r="C64" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D64" s="24" t="inlineStr">
+      <c r="C64" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D64" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="24" t="inlineStr">
+      <c r="A65" s="37" t="inlineStr">
         <is>
           <t>60039277</t>
         </is>
       </c>
-      <c r="B65" s="24" t="inlineStr">
+      <c r="B65" s="37" t="inlineStr">
         <is>
           <t>TA–8PSV4236–Overhaul</t>
         </is>
       </c>
-      <c r="C65" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D65" s="24" t="inlineStr">
+      <c r="C65" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D65" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="24" t="inlineStr">
+      <c r="A66" s="37" t="inlineStr">
         <is>
           <t>60039278</t>
         </is>
       </c>
-      <c r="B66" s="24" t="inlineStr">
+      <c r="B66" s="37" t="inlineStr">
         <is>
           <t>TA–8PSV4912–Overhaul</t>
         </is>
       </c>
-      <c r="C66" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D66" s="24" t="inlineStr">
+      <c r="C66" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D66" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="24" t="inlineStr">
+      <c r="A67" s="37" t="inlineStr">
         <is>
           <t>60039279</t>
         </is>
       </c>
-      <c r="B67" s="24" t="inlineStr">
+      <c r="B67" s="37" t="inlineStr">
         <is>
           <t>TA–8PSV5199–Overhaul</t>
         </is>
       </c>
-      <c r="C67" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D67" s="24" t="inlineStr">
+      <c r="C67" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D67" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="24" t="inlineStr">
+      <c r="A68" s="37" t="inlineStr">
         <is>
           <t>60039280</t>
         </is>
       </c>
-      <c r="B68" s="24" t="inlineStr">
+      <c r="B68" s="37" t="inlineStr">
         <is>
           <t>TA–8PSV5909–Overhaul</t>
         </is>
       </c>
-      <c r="C68" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D68" s="24" t="inlineStr">
+      <c r="C68" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D68" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="24" t="inlineStr">
+      <c r="A69" s="37" t="inlineStr">
         <is>
           <t>60041236</t>
         </is>
       </c>
-      <c r="B69" s="24" t="inlineStr">
+      <c r="B69" s="37" t="inlineStr">
         <is>
           <t>TA - A2 Valve Survey Followup Repairs</t>
         </is>
       </c>
-      <c r="C69" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D69" s="24" t="inlineStr">
+      <c r="C69" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D69" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="24" t="inlineStr">
+      <c r="A70" s="37" t="inlineStr">
         <is>
           <t>60041401</t>
         </is>
       </c>
-      <c r="B70" s="24" t="inlineStr">
+      <c r="B70" s="37" t="inlineStr">
         <is>
           <t>TA - C410A Replace Head and Others</t>
         </is>
       </c>
-      <c r="C70" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D70" s="24" t="inlineStr">
+      <c r="C70" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D70" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="24" t="inlineStr">
+      <c r="A71" s="37" t="inlineStr">
         <is>
           <t>60041402</t>
         </is>
       </c>
-      <c r="B71" s="24" t="inlineStr">
+      <c r="B71" s="37" t="inlineStr">
         <is>
           <t>TA - C410B Replace Head and Others</t>
         </is>
       </c>
-      <c r="C71" s="24" t="inlineStr">
-        <is>
-          <t>TA70017</t>
-        </is>
-      </c>
-      <c r="D71" s="24" t="inlineStr">
+      <c r="C71" s="37" t="inlineStr">
+        <is>
+          <t>TA70017</t>
+        </is>
+      </c>
+      <c r="D71" s="37" t="inlineStr">
         <is>
           <t>AMM2</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="24" t="inlineStr">
+      <c r="A72" s="37" t="inlineStr">
         <is>
           <t>60041403</t>
         </is>
       </c>
-      <c r="B72" s="24" t="inlineStr">
+      <c r="B72" s="37" t="inlineStr">
         <is>
           <t>TA - Cat Combustor</t>
         </is>
       </c>
-      <c r="C72" s="24" t="inlineStr">
+      <c r="C72" s="37" t="inlineStr">
         <is>
           <t>TA70019</t>
         </is>
       </c>
-      <c r="D72" s="24" t="inlineStr">
+      <c r="D72" s="37" t="inlineStr">
         <is>
           <t>NA01</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="24" t="inlineStr">
+      <c r="A73" s="37" t="inlineStr">
         <is>
           <t>60041408</t>
         </is>
       </c>
-      <c r="B73" s="24" t="inlineStr">
+      <c r="B73" s="37" t="inlineStr">
         <is>
           <t>TA–3PSV4333–Overhaul</t>
         </is>
       </c>
-      <c r="C73" s="24" t="inlineStr">
+      <c r="C73" s="37" t="inlineStr">
         <is>
           <t>TA70019</t>
         </is>
       </c>
-      <c r="D73" s="24" t="inlineStr">
+      <c r="D73" s="37" t="inlineStr">
         <is>
           <t>NA01</t>
         </is>
@@ -4260,154 +4675,178 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B25"/>
+  <dimension ref="B1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="104" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="38" t="inlineStr">
         <is>
           <t>CF Turnaround Timesheet — FAQ</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>Filling it out (the basics)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="B4" s="40" t="inlineStr">
+        <is>
+          <t>• Fill only the YELLOW cells. Grey cells (CF ID, Activity Type, Total, Work Order Description) fill in automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="B5" s="40" t="inlineStr">
+        <is>
+          <t>• Pick names, trades and work orders from the dropdowns so they always match SAP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="B6" s="40" t="inlineStr">
+        <is>
+          <t>• Enter RT and DT hours — the Total column adds them for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>Work order formatting</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="B4" s="27" t="inlineStr">
-        <is>
-          <t>• The Work Order column pulls valid SAP order numbers from the 'Work Orders' tab (refreshed daily from the IW29 export). Pick from the dropdown so the number always matches SAP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>• Need to add detail? Use the 'Work Order Description' column or the header WORK ORDER box — both accept free text and expand.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="27" t="inlineStr">
-        <is>
-          <t>• A work order number that isn't on the 'Work Orders' tab means it's not in today's IW29 pull — check the revision/date or ask the planner before entering it manually.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="B8" s="26" t="inlineStr">
+    <row r="9" ht="30" customHeight="1">
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>• The Work Order dropdown pulls valid SAP orders from the 'Work Orders' tab (refreshed daily from IW29).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t>• Its description auto-fills next to it. Need more detail? Use the Notes column or the Notes box at the bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="B11" s="40" t="inlineStr">
+        <is>
+          <t>• A work order not in the list isn't in today's IW29 pull — check with the planner before entering it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="39" t="inlineStr">
         <is>
           <t>Adding employees</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="27" t="inlineStr">
-        <is>
-          <t>• Go to the 'Reference' tab, EMPLOYEES block. Add the person's Name, CF ID, default Work Center and default Trade on the next empty row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="27" t="inlineStr">
-        <is>
-          <t>• The Employee Name dropdown on the Timesheet updates automatically (the list has room for ~200 names).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="27" t="inlineStr">
-        <is>
-          <t>• CF ID auto-fills on the Timesheet once the name is chosen. If you see a red cell / '?', the name isn't in Reference yet — add it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="B13" s="26" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>• On the 'Reference' tab, EMPLOYEES block, add Name, CF ID, Work Center and default Trade on the next empty row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="40" t="inlineStr">
+        <is>
+          <t>• The Employee Name dropdown updates automatically. CF ID auto-fills on the Timesheet once the name is chosen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="B16" s="40" t="inlineStr">
+        <is>
+          <t>• A red name cell / '?' means the person isn't in Reference yet — add them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>Adding roles / trades</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="27" t="inlineStr">
-        <is>
-          <t>• On the 'Reference' tab, TRADES block, add the Trade/Position, its SAP Activity Type (e.g. CI203), the Activity Type Description, and Work Center.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>• Straight time vs double time are separate activity types (…ST vs …DT) — add a row for each rate you need.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="B16" s="27" t="inlineStr">
-        <is>
-          <t>• The Activity Type on the Timesheet auto-fills from the trade you pick. A red cell / '?' means that trade isn't mapped yet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>Checks built into the sheet</t>
-        </is>
-      </c>
-    </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="27" t="inlineStr">
-        <is>
-          <t>• Red employee cell = name not found in Reference. Red trade cell = trade not mapped to an activity type.</t>
+      <c r="B19" s="40" t="inlineStr">
+        <is>
+          <t>• On 'Reference', TRADES block, add Trade/Position, SAP Activity Type (e.g. CI203), the description, and Work Center.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="27" t="inlineStr">
-        <is>
-          <t>• Enter each person's Lenel swipe hours in the 'Lenel Hours' column; the 'Deviation' column turns red when booked hours don't match the swipe.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="27" t="inlineStr">
-        <is>
-          <t>• Total Hours turns red if it exceeds 16 or is negative; it turns amber if RT + DT don't add up to the Total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="27" t="inlineStr">
-        <is>
-          <t>• Use the 'Swipe Deviation Reason' and 'Hold Up Type' dropdowns to explain any approved deviation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="26" t="inlineStr">
-        <is>
-          <t>Daily workflow (reference)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="B25" s="27" t="inlineStr">
-        <is>
-          <t>1. Planner pulls IW37N/IW29 → paste into 'Work Orders' tab.  2. Pull Lenel swipe export.  3. Receive timecards.  4. Fill the Timesheet + Lenel Hours.  5. Work through red flags &amp; swipe deviations.  6. Allocate hours to op steps.  7. Export to Excel / pivot for approvals.  8. Upload to SAP (split by op step).</t>
+      <c r="B20" s="40" t="inlineStr">
+        <is>
+          <t>• Straight time and double time are separate activity types (…ST vs …DT) — add a row for each rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="B21" s="40" t="inlineStr">
+        <is>
+          <t>• A red trade cell / '?' means that trade isn't mapped yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="B23" s="39" t="inlineStr">
+        <is>
+          <t>Reconciliation columns (for Hillary)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="40" t="inlineStr">
+        <is>
+          <t>• Columns to the right of Notes are collapsed. Click the ► above column M to expand Lenel Hrs, Deviation, Swipe Reason and Hold Up Type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="B25" s="40" t="inlineStr">
+        <is>
+          <t>• Enter each person's Lenel swipe hours; Deviation (Total − Lenel) turns red when they don't match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="B26" s="40" t="inlineStr">
+        <is>
+          <t>• Use Swipe Deviation Reason and Hold Up Type to explain any approved difference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="B28" s="39" t="inlineStr">
+        <is>
+          <t>Daily workflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="B29" s="40" t="inlineStr">
+        <is>
+          <t>1. Planner pulls IW37N/IW29 → 'Work Orders' tab.  2. Pull Lenel export.  3. Receive timecards.  4. Fill Timesheet + Lenel Hrs.  5. Clear red flags &amp; swipe deviations.  6. Allocate hours to op steps.  7. Export / pivot for approvals.  8. Upload to SAP (split by op step).</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/CF-Timesheet/CF_Timesheet_Template.xlsx
+++ b/CF-Timesheet/CF_Timesheet_Template.xlsx
@@ -42,7 +42,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-1009]d/mmm/yy;@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -115,8 +115,55 @@
       <sz val="8"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00015846"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="006B7A77"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00B7791F"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000A6E5A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F2A28"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00015846"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -177,8 +224,23 @@
         <bgColor theme="4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00015846"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000C7B1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000A6E5A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -430,12 +492,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FFFFFF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -680,6 +756,44 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="11" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="12" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1098,7 +1212,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1143000" cy="571500"/>
+    <ext cx="1028700" cy="495300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -9289,7 +9403,7 @@
       <c r="EO4" s="21" t="n"/>
       <c r="EP4" s="21" t="n"/>
     </row>
-    <row r="5" ht="18" customFormat="1" customHeight="1" s="17">
+    <row r="5" ht="22" customFormat="1" customHeight="1" s="17">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Blank</t>
@@ -9300,17 +9414,17 @@
           <t>Blank</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>CF INDUSTRIES  —  TA TIMESHEET</t>
-        </is>
-      </c>
-      <c r="D5" s="32" t="inlineStr">
+      <c r="C5" s="78" t="inlineStr">
+        <is>
+          <t>CF INDUSTRIES TIMESHEET</t>
+        </is>
+      </c>
+      <c r="D5" s="79" t="inlineStr">
         <is>
           <t>Ver. 1.7.1</t>
         </is>
       </c>
-      <c r="H5" s="29" t="inlineStr">
+      <c r="H5" s="80" t="inlineStr">
         <is>
           <t>POPULATE YELLOW HIGHLIGHTED CELLS</t>
         </is>
@@ -9442,12 +9556,12 @@
           <t>Blank</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="81" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="81" t="inlineStr">
         <is>
           <t>Shift</t>
         </is>
@@ -9590,7 +9704,7 @@
           <t>Day</t>
         </is>
       </c>
-      <c r="H7" s="34" t="inlineStr">
+      <c r="H7" s="82" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
@@ -9762,7 +9876,7 @@
         <f>IF(C7="","",TEXT(C7,"dddd"))</f>
         <v/>
       </c>
-      <c r="H8" s="34" t="inlineStr">
+      <c r="H8" s="82" t="inlineStr">
         <is>
           <t>Job Number</t>
         </is>
@@ -9931,7 +10045,7 @@
         </is>
       </c>
       <c r="C9" s="21" t="n"/>
-      <c r="H9" s="34" t="inlineStr">
+      <c r="H9" s="82" t="inlineStr">
         <is>
           <t>Job Desc (not req'd)</t>
         </is>
@@ -10087,7 +10201,7 @@
           <t>Blank</t>
         </is>
       </c>
-      <c r="H10" s="49" t="inlineStr">
+      <c r="H10" s="83" t="inlineStr">
         <is>
           <t>Task Number</t>
         </is>
@@ -10232,7 +10346,7 @@
       <c r="EP10" s="51" t="n"/>
       <c r="EQ10" s="51" t="n"/>
     </row>
-    <row r="11" ht="77.40000000000001" customFormat="1" customHeight="1" s="17">
+    <row r="11" ht="46" customFormat="1" customHeight="1" s="17">
       <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Summary</t>
@@ -10243,643 +10357,643 @@
           <t>Blank</t>
         </is>
       </c>
-      <c r="C11" s="45" t="inlineStr">
+      <c r="C11" s="84" t="inlineStr">
         <is>
           <t>Employee Name</t>
         </is>
       </c>
-      <c r="D11" s="45" t="inlineStr">
+      <c r="D11" s="84" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="E11" s="45" t="inlineStr">
+      <c r="E11" s="84" t="inlineStr">
         <is>
           <t>Total Hours</t>
         </is>
       </c>
-      <c r="F11" s="45" t="inlineStr">
+      <c r="F11" s="84" t="inlineStr">
         <is>
           <t>RT Hours</t>
         </is>
       </c>
-      <c r="G11" s="45" t="inlineStr">
+      <c r="G11" s="84" t="inlineStr">
         <is>
           <t>DT Hours</t>
         </is>
       </c>
-      <c r="H11" s="46" t="inlineStr">
+      <c r="H11" s="84" t="inlineStr">
         <is>
           <t>Work Location</t>
         </is>
       </c>
-      <c r="I11" s="46" t="inlineStr">
+      <c r="I11" s="84" t="inlineStr">
         <is>
           <t>Swipe Deviation (if Appr Offsite is used as Hold Up)</t>
         </is>
       </c>
-      <c r="J11" s="46" t="inlineStr">
+      <c r="J11" s="84" t="inlineStr">
         <is>
           <t>Special Rate Considerations (Free Text)</t>
         </is>
       </c>
-      <c r="K11" s="66" t="inlineStr">
+      <c r="K11" s="84" t="inlineStr">
         <is>
           <t>Daily LOA</t>
         </is>
       </c>
-      <c r="L11" s="66" t="inlineStr">
+      <c r="L11" s="84" t="inlineStr">
         <is>
           <t>Which Column?</t>
         </is>
       </c>
-      <c r="M11" s="68" t="inlineStr">
+      <c r="M11" s="84" t="inlineStr">
         <is>
           <t>Meal $$</t>
         </is>
       </c>
-      <c r="N11" s="68" t="inlineStr">
+      <c r="N11" s="84" t="inlineStr">
         <is>
           <t>Which Column?</t>
         </is>
       </c>
-      <c r="O11" s="71" t="inlineStr">
+      <c r="O11" s="84" t="inlineStr">
         <is>
           <t>Meal Order</t>
         </is>
       </c>
-      <c r="P11" s="71" t="inlineStr">
+      <c r="P11" s="84" t="inlineStr">
         <is>
           <t>Which Column?</t>
         </is>
       </c>
-      <c r="Q11" s="47" t="inlineStr">
+      <c r="Q11" s="85" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="R11" s="45" t="inlineStr">
+      <c r="R11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="S11" s="45" t="inlineStr">
+      <c r="S11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="T11" s="45" t="inlineStr">
+      <c r="T11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="U11" s="45" t="inlineStr">
+      <c r="U11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="V11" s="57" t="n"/>
-      <c r="W11" s="46" t="inlineStr">
+      <c r="W11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="X11" s="45" t="inlineStr">
+      <c r="X11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="Y11" s="45" t="inlineStr">
+      <c r="Y11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="Z11" s="45" t="inlineStr">
+      <c r="Z11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="AA11" s="45" t="inlineStr">
+      <c r="AA11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="AB11" s="55" t="n"/>
-      <c r="AC11" s="46" t="inlineStr">
+      <c r="AC11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="AD11" s="45" t="inlineStr">
+      <c r="AD11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="AE11" s="45" t="inlineStr">
+      <c r="AE11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="AF11" s="45" t="inlineStr">
+      <c r="AF11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="AG11" s="45" t="inlineStr">
+      <c r="AG11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="AH11" s="55" t="n"/>
-      <c r="AI11" s="46" t="inlineStr">
+      <c r="AI11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="AJ11" s="45" t="inlineStr">
+      <c r="AJ11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="AK11" s="45" t="inlineStr">
+      <c r="AK11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="AL11" s="45" t="inlineStr">
+      <c r="AL11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="AM11" s="45" t="inlineStr">
+      <c r="AM11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="AN11" s="55" t="n"/>
-      <c r="AO11" s="46" t="inlineStr">
+      <c r="AO11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="AP11" s="45" t="inlineStr">
+      <c r="AP11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="AQ11" s="45" t="inlineStr">
+      <c r="AQ11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="AR11" s="45" t="inlineStr">
+      <c r="AR11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="AS11" s="45" t="inlineStr">
+      <c r="AS11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="AT11" s="55" t="n"/>
-      <c r="AU11" s="46" t="inlineStr">
+      <c r="AU11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="AV11" s="45" t="inlineStr">
+      <c r="AV11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="AW11" s="45" t="inlineStr">
+      <c r="AW11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="AX11" s="45" t="inlineStr">
+      <c r="AX11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="AY11" s="45" t="inlineStr">
+      <c r="AY11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="AZ11" s="55" t="n"/>
-      <c r="BA11" s="46" t="inlineStr">
+      <c r="BA11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BB11" s="45" t="inlineStr">
+      <c r="BB11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="BC11" s="45" t="inlineStr">
+      <c r="BC11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="BD11" s="45" t="inlineStr">
+      <c r="BD11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="BE11" s="45" t="inlineStr">
+      <c r="BE11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="BF11" s="55" t="n"/>
-      <c r="BG11" s="46" t="inlineStr">
+      <c r="BG11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BH11" s="45" t="inlineStr">
+      <c r="BH11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="BI11" s="45" t="inlineStr">
+      <c r="BI11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="BJ11" s="45" t="inlineStr">
+      <c r="BJ11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="BK11" s="45" t="inlineStr">
+      <c r="BK11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="BL11" s="55" t="n"/>
-      <c r="BM11" s="46" t="inlineStr">
+      <c r="BM11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BN11" s="45" t="inlineStr">
+      <c r="BN11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="BO11" s="45" t="inlineStr">
+      <c r="BO11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="BP11" s="45" t="inlineStr">
+      <c r="BP11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="BQ11" s="45" t="inlineStr">
+      <c r="BQ11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="BR11" s="55" t="n"/>
-      <c r="BS11" s="46" t="inlineStr">
+      <c r="BS11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BT11" s="45" t="inlineStr">
+      <c r="BT11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="BU11" s="45" t="inlineStr">
+      <c r="BU11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="BV11" s="45" t="inlineStr">
+      <c r="BV11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="BW11" s="45" t="inlineStr">
+      <c r="BW11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="BX11" s="55" t="n"/>
-      <c r="BY11" s="46" t="inlineStr">
+      <c r="BY11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="BZ11" s="45" t="inlineStr">
+      <c r="BZ11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="CA11" s="45" t="inlineStr">
+      <c r="CA11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="CB11" s="45" t="inlineStr">
+      <c r="CB11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="CC11" s="45" t="inlineStr">
+      <c r="CC11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="CD11" s="55" t="n"/>
-      <c r="CE11" s="46" t="inlineStr">
+      <c r="CE11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="CF11" s="45" t="inlineStr">
+      <c r="CF11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="CG11" s="45" t="inlineStr">
+      <c r="CG11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="CH11" s="45" t="inlineStr">
+      <c r="CH11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="CI11" s="45" t="inlineStr">
+      <c r="CI11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="CJ11" s="55" t="n"/>
-      <c r="CK11" s="46" t="inlineStr">
+      <c r="CK11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="CL11" s="45" t="inlineStr">
+      <c r="CL11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="CM11" s="45" t="inlineStr">
+      <c r="CM11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="CN11" s="45" t="inlineStr">
+      <c r="CN11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="CO11" s="45" t="inlineStr">
+      <c r="CO11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="CP11" s="55" t="n"/>
-      <c r="CQ11" s="46" t="inlineStr">
+      <c r="CQ11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="CR11" s="45" t="inlineStr">
+      <c r="CR11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="CS11" s="45" t="inlineStr">
+      <c r="CS11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="CT11" s="45" t="inlineStr">
+      <c r="CT11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="CU11" s="45" t="inlineStr">
+      <c r="CU11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="CV11" s="55" t="n"/>
-      <c r="CW11" s="46" t="inlineStr">
+      <c r="CW11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="CX11" s="45" t="inlineStr">
+      <c r="CX11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="CY11" s="45" t="inlineStr">
+      <c r="CY11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="CZ11" s="45" t="inlineStr">
+      <c r="CZ11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="DA11" s="45" t="inlineStr">
+      <c r="DA11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="DB11" s="55" t="n"/>
-      <c r="DC11" s="46" t="inlineStr">
+      <c r="DC11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="DD11" s="45" t="inlineStr">
+      <c r="DD11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="DE11" s="45" t="inlineStr">
+      <c r="DE11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="DF11" s="45" t="inlineStr">
+      <c r="DF11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="DG11" s="45" t="inlineStr">
+      <c r="DG11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="DH11" s="55" t="n"/>
-      <c r="DI11" s="46" t="inlineStr">
+      <c r="DI11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="DJ11" s="45" t="inlineStr">
+      <c r="DJ11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="DK11" s="45" t="inlineStr">
+      <c r="DK11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="DL11" s="45" t="inlineStr">
+      <c r="DL11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="DM11" s="45" t="inlineStr">
+      <c r="DM11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="DN11" s="55" t="n"/>
-      <c r="DO11" s="46" t="inlineStr">
+      <c r="DO11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="DP11" s="45" t="inlineStr">
+      <c r="DP11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="DQ11" s="45" t="inlineStr">
+      <c r="DQ11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="DR11" s="45" t="inlineStr">
+      <c r="DR11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="DS11" s="45" t="inlineStr">
+      <c r="DS11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="DT11" s="55" t="n"/>
-      <c r="DU11" s="46" t="inlineStr">
+      <c r="DU11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="DV11" s="45" t="inlineStr">
+      <c r="DV11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="DW11" s="45" t="inlineStr">
+      <c r="DW11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="DX11" s="45" t="inlineStr">
+      <c r="DX11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="DY11" s="45" t="inlineStr">
+      <c r="DY11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="DZ11" s="55" t="n"/>
-      <c r="EA11" s="46" t="inlineStr">
+      <c r="EA11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="EB11" s="45" t="inlineStr">
+      <c r="EB11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="EC11" s="45" t="inlineStr">
+      <c r="EC11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="ED11" s="45" t="inlineStr">
+      <c r="ED11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="EE11" s="45" t="inlineStr">
+      <c r="EE11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="EF11" s="55" t="n"/>
-      <c r="EG11" s="46" t="inlineStr">
+      <c r="EG11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="EH11" s="45" t="inlineStr">
+      <c r="EH11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="EI11" s="45" t="inlineStr">
+      <c r="EI11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="EJ11" s="45" t="inlineStr">
+      <c r="EJ11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="EK11" s="45" t="inlineStr">
+      <c r="EK11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
       </c>
       <c r="EL11" s="55" t="n"/>
-      <c r="EM11" s="46" t="inlineStr">
+      <c r="EM11" s="84" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="EN11" s="45" t="inlineStr">
+      <c r="EN11" s="84" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="EO11" s="45" t="inlineStr">
+      <c r="EO11" s="84" t="inlineStr">
         <is>
           <t>Hold Up RT</t>
         </is>
       </c>
-      <c r="EP11" s="45" t="inlineStr">
+      <c r="EP11" s="84" t="inlineStr">
         <is>
           <t>Hold Up DT</t>
         </is>
       </c>
-      <c r="EQ11" s="45" t="inlineStr">
+      <c r="EQ11" s="84" t="inlineStr">
         <is>
           <t>Hold Up Type</t>
         </is>
@@ -14235,388 +14349,388 @@
           <t>Blank</t>
         </is>
       </c>
-      <c r="E33" s="25">
+      <c r="E33" s="86">
         <f>SUM(E12:E32)</f>
         <v/>
       </c>
-      <c r="F33" s="25">
+      <c r="F33" s="86">
         <f>SUM(F12:F32)</f>
         <v/>
       </c>
-      <c r="G33" s="25">
+      <c r="G33" s="86">
         <f>SUM(G12:G32)</f>
         <v/>
       </c>
-      <c r="Q33" s="27">
+      <c r="Q33" s="87">
         <f>SUM(Q12:Q32)</f>
         <v/>
       </c>
-      <c r="R33" s="25">
+      <c r="R33" s="86">
         <f>SUM(R12:R32)</f>
         <v/>
       </c>
-      <c r="S33" s="25">
+      <c r="S33" s="86">
         <f>SUM(S12:S32)</f>
         <v/>
       </c>
-      <c r="T33" s="25">
+      <c r="T33" s="86">
         <f>SUM(T12:T32)</f>
         <v/>
       </c>
       <c r="V33" s="60" t="n"/>
-      <c r="W33" s="25">
+      <c r="W33" s="86">
         <f>SUM(W12:W32)</f>
         <v/>
       </c>
-      <c r="X33" s="25">
+      <c r="X33" s="86">
         <f>SUM(X12:X32)</f>
         <v/>
       </c>
-      <c r="Y33" s="25">
+      <c r="Y33" s="86">
         <f>SUM(Y12:Y32)</f>
         <v/>
       </c>
-      <c r="Z33" s="25">
+      <c r="Z33" s="86">
         <f>SUM(Z12:Z32)</f>
         <v/>
       </c>
       <c r="AB33" s="60" t="n"/>
-      <c r="AC33" s="25">
+      <c r="AC33" s="86">
         <f>SUM(AC12:AC32)</f>
         <v/>
       </c>
-      <c r="AD33" s="25">
+      <c r="AD33" s="86">
         <f>SUM(AD12:AD32)</f>
         <v/>
       </c>
-      <c r="AE33" s="25">
+      <c r="AE33" s="86">
         <f>SUM(AE12:AE32)</f>
         <v/>
       </c>
-      <c r="AF33" s="25">
+      <c r="AF33" s="86">
         <f>SUM(AF12:AF32)</f>
         <v/>
       </c>
       <c r="AH33" s="60" t="n"/>
-      <c r="AI33" s="25">
+      <c r="AI33" s="86">
         <f>SUM(AI12:AI32)</f>
         <v/>
       </c>
-      <c r="AJ33" s="25">
+      <c r="AJ33" s="86">
         <f>SUM(AJ12:AJ32)</f>
         <v/>
       </c>
-      <c r="AK33" s="25">
+      <c r="AK33" s="86">
         <f>SUM(AK12:AK32)</f>
         <v/>
       </c>
-      <c r="AL33" s="25">
+      <c r="AL33" s="86">
         <f>SUM(AL12:AL32)</f>
         <v/>
       </c>
       <c r="AN33" s="60" t="n"/>
-      <c r="AO33" s="25">
+      <c r="AO33" s="86">
         <f>SUM(AO12:AO32)</f>
         <v/>
       </c>
-      <c r="AP33" s="25">
+      <c r="AP33" s="86">
         <f>SUM(AP12:AP32)</f>
         <v/>
       </c>
-      <c r="AQ33" s="25">
+      <c r="AQ33" s="86">
         <f>SUM(AQ12:AQ32)</f>
         <v/>
       </c>
-      <c r="AR33" s="25">
+      <c r="AR33" s="86">
         <f>SUM(AR12:AR32)</f>
         <v/>
       </c>
       <c r="AT33" s="60" t="n"/>
-      <c r="AU33" s="25">
+      <c r="AU33" s="86">
         <f>SUM(AU12:AU32)</f>
         <v/>
       </c>
-      <c r="AV33" s="25">
+      <c r="AV33" s="86">
         <f>SUM(AV12:AV32)</f>
         <v/>
       </c>
-      <c r="AW33" s="25">
+      <c r="AW33" s="86">
         <f>SUM(AW12:AW32)</f>
         <v/>
       </c>
-      <c r="AX33" s="25">
+      <c r="AX33" s="86">
         <f>SUM(AX12:AX32)</f>
         <v/>
       </c>
       <c r="AZ33" s="60" t="n"/>
-      <c r="BA33" s="25">
+      <c r="BA33" s="86">
         <f>SUM(BA12:BA32)</f>
         <v/>
       </c>
-      <c r="BB33" s="25">
+      <c r="BB33" s="86">
         <f>SUM(BB12:BB32)</f>
         <v/>
       </c>
-      <c r="BC33" s="25">
+      <c r="BC33" s="86">
         <f>SUM(BC12:BC32)</f>
         <v/>
       </c>
-      <c r="BD33" s="25">
+      <c r="BD33" s="86">
         <f>SUM(BD12:BD32)</f>
         <v/>
       </c>
       <c r="BF33" s="60" t="n"/>
-      <c r="BG33" s="25">
+      <c r="BG33" s="86">
         <f>SUM(BG12:BG32)</f>
         <v/>
       </c>
-      <c r="BH33" s="25">
+      <c r="BH33" s="86">
         <f>SUM(BH12:BH32)</f>
         <v/>
       </c>
-      <c r="BI33" s="25">
+      <c r="BI33" s="86">
         <f>SUM(BI12:BI32)</f>
         <v/>
       </c>
-      <c r="BJ33" s="25">
+      <c r="BJ33" s="86">
         <f>SUM(BJ12:BJ32)</f>
         <v/>
       </c>
       <c r="BL33" s="60" t="n"/>
-      <c r="BM33" s="25">
+      <c r="BM33" s="86">
         <f>SUM(BM12:BM32)</f>
         <v/>
       </c>
-      <c r="BN33" s="25">
+      <c r="BN33" s="86">
         <f>SUM(BN12:BN32)</f>
         <v/>
       </c>
-      <c r="BO33" s="25">
+      <c r="BO33" s="86">
         <f>SUM(BO12:BO32)</f>
         <v/>
       </c>
-      <c r="BP33" s="25">
+      <c r="BP33" s="86">
         <f>SUM(BP12:BP32)</f>
         <v/>
       </c>
       <c r="BR33" s="60" t="n"/>
-      <c r="BS33" s="25">
+      <c r="BS33" s="86">
         <f>SUM(BS12:BS32)</f>
         <v/>
       </c>
-      <c r="BT33" s="25">
+      <c r="BT33" s="86">
         <f>SUM(BT12:BT32)</f>
         <v/>
       </c>
-      <c r="BU33" s="25">
+      <c r="BU33" s="86">
         <f>SUM(BU12:BU32)</f>
         <v/>
       </c>
-      <c r="BV33" s="25">
+      <c r="BV33" s="86">
         <f>SUM(BV12:BV32)</f>
         <v/>
       </c>
       <c r="BX33" s="60" t="n"/>
-      <c r="BY33" s="25">
+      <c r="BY33" s="86">
         <f>SUM(BY12:BY32)</f>
         <v/>
       </c>
-      <c r="BZ33" s="25">
+      <c r="BZ33" s="86">
         <f>SUM(BZ12:BZ32)</f>
         <v/>
       </c>
-      <c r="CA33" s="25">
+      <c r="CA33" s="86">
         <f>SUM(CA12:CA32)</f>
         <v/>
       </c>
-      <c r="CB33" s="25">
+      <c r="CB33" s="86">
         <f>SUM(CB12:CB32)</f>
         <v/>
       </c>
       <c r="CD33" s="60" t="n"/>
-      <c r="CE33" s="25">
+      <c r="CE33" s="86">
         <f>SUM(CE12:CE32)</f>
         <v/>
       </c>
-      <c r="CF33" s="25">
+      <c r="CF33" s="86">
         <f>SUM(CF12:CF32)</f>
         <v/>
       </c>
-      <c r="CG33" s="25">
+      <c r="CG33" s="86">
         <f>SUM(CG12:CG32)</f>
         <v/>
       </c>
-      <c r="CH33" s="25">
+      <c r="CH33" s="86">
         <f>SUM(CH12:CH32)</f>
         <v/>
       </c>
       <c r="CJ33" s="60" t="n"/>
-      <c r="CK33" s="25">
+      <c r="CK33" s="86">
         <f>SUM(CK12:CK32)</f>
         <v/>
       </c>
-      <c r="CL33" s="25">
+      <c r="CL33" s="86">
         <f>SUM(CL12:CL32)</f>
         <v/>
       </c>
-      <c r="CM33" s="25">
+      <c r="CM33" s="86">
         <f>SUM(CM12:CM32)</f>
         <v/>
       </c>
-      <c r="CN33" s="25">
+      <c r="CN33" s="86">
         <f>SUM(CN12:CN32)</f>
         <v/>
       </c>
       <c r="CP33" s="60" t="n"/>
-      <c r="CQ33" s="25">
+      <c r="CQ33" s="86">
         <f>SUM(CQ12:CQ32)</f>
         <v/>
       </c>
-      <c r="CR33" s="25">
+      <c r="CR33" s="86">
         <f>SUM(CR12:CR32)</f>
         <v/>
       </c>
-      <c r="CS33" s="25">
+      <c r="CS33" s="86">
         <f>SUM(CS12:CS32)</f>
         <v/>
       </c>
-      <c r="CT33" s="25">
+      <c r="CT33" s="86">
         <f>SUM(CT12:CT32)</f>
         <v/>
       </c>
       <c r="CV33" s="60" t="n"/>
-      <c r="CW33" s="25">
+      <c r="CW33" s="86">
         <f>SUM(CW12:CW32)</f>
         <v/>
       </c>
-      <c r="CX33" s="25">
+      <c r="CX33" s="86">
         <f>SUM(CX12:CX32)</f>
         <v/>
       </c>
-      <c r="CY33" s="25">
+      <c r="CY33" s="86">
         <f>SUM(CY12:CY32)</f>
         <v/>
       </c>
-      <c r="CZ33" s="25">
+      <c r="CZ33" s="86">
         <f>SUM(CZ12:CZ32)</f>
         <v/>
       </c>
       <c r="DB33" s="60" t="n"/>
-      <c r="DC33" s="25">
+      <c r="DC33" s="86">
         <f>SUM(DC12:DC32)</f>
         <v/>
       </c>
-      <c r="DD33" s="25">
+      <c r="DD33" s="86">
         <f>SUM(DD12:DD32)</f>
         <v/>
       </c>
-      <c r="DE33" s="25">
+      <c r="DE33" s="86">
         <f>SUM(DE12:DE32)</f>
         <v/>
       </c>
-      <c r="DF33" s="25">
+      <c r="DF33" s="86">
         <f>SUM(DF12:DF32)</f>
         <v/>
       </c>
       <c r="DH33" s="60" t="n"/>
-      <c r="DI33" s="25">
+      <c r="DI33" s="86">
         <f>SUM(DI12:DI32)</f>
         <v/>
       </c>
-      <c r="DJ33" s="25">
+      <c r="DJ33" s="86">
         <f>SUM(DJ12:DJ32)</f>
         <v/>
       </c>
-      <c r="DK33" s="25">
+      <c r="DK33" s="86">
         <f>SUM(DK12:DK32)</f>
         <v/>
       </c>
-      <c r="DL33" s="25">
+      <c r="DL33" s="86">
         <f>SUM(DL12:DL32)</f>
         <v/>
       </c>
       <c r="DN33" s="60" t="n"/>
-      <c r="DO33" s="25">
+      <c r="DO33" s="86">
         <f>SUM(DO12:DO32)</f>
         <v/>
       </c>
-      <c r="DP33" s="25">
+      <c r="DP33" s="86">
         <f>SUM(DP12:DP32)</f>
         <v/>
       </c>
-      <c r="DQ33" s="25">
+      <c r="DQ33" s="86">
         <f>SUM(DQ12:DQ32)</f>
         <v/>
       </c>
-      <c r="DR33" s="25">
+      <c r="DR33" s="86">
         <f>SUM(DR12:DR32)</f>
         <v/>
       </c>
       <c r="DT33" s="60" t="n"/>
-      <c r="DU33" s="25">
+      <c r="DU33" s="86">
         <f>SUM(DU12:DU32)</f>
         <v/>
       </c>
-      <c r="DV33" s="25">
+      <c r="DV33" s="86">
         <f>SUM(DV12:DV32)</f>
         <v/>
       </c>
-      <c r="DW33" s="25">
+      <c r="DW33" s="86">
         <f>SUM(DW12:DW32)</f>
         <v/>
       </c>
-      <c r="DX33" s="25">
+      <c r="DX33" s="86">
         <f>SUM(DX12:DX32)</f>
         <v/>
       </c>
       <c r="DZ33" s="60" t="n"/>
-      <c r="EA33" s="25">
+      <c r="EA33" s="86">
         <f>SUM(EA12:EA32)</f>
         <v/>
       </c>
-      <c r="EB33" s="25">
+      <c r="EB33" s="86">
         <f>SUM(EB12:EB32)</f>
         <v/>
       </c>
-      <c r="EC33" s="25">
+      <c r="EC33" s="86">
         <f>SUM(EC12:EC32)</f>
         <v/>
       </c>
-      <c r="ED33" s="25">
+      <c r="ED33" s="86">
         <f>SUM(ED12:ED32)</f>
         <v/>
       </c>
       <c r="EF33" s="60" t="n"/>
-      <c r="EG33" s="25">
+      <c r="EG33" s="86">
         <f>SUM(EG12:EG32)</f>
         <v/>
       </c>
-      <c r="EH33" s="25">
+      <c r="EH33" s="86">
         <f>SUM(EH12:EH32)</f>
         <v/>
       </c>
-      <c r="EI33" s="25">
+      <c r="EI33" s="86">
         <f>SUM(EI12:EI32)</f>
         <v/>
       </c>
-      <c r="EJ33" s="25">
+      <c r="EJ33" s="86">
         <f>SUM(EJ12:EJ32)</f>
         <v/>
       </c>
       <c r="EL33" s="60" t="n"/>
-      <c r="EM33" s="25">
+      <c r="EM33" s="86">
         <f>SUM(EM12:EM32)</f>
         <v/>
       </c>
-      <c r="EN33" s="25">
+      <c r="EN33" s="86">
         <f>SUM(EN12:EN32)</f>
         <v/>
       </c>
-      <c r="EO33" s="25">
+      <c r="EO33" s="86">
         <f>SUM(EO12:EO32)</f>
         <v/>
       </c>
-      <c r="EP33" s="25">
+      <c r="EP33" s="86">
         <f>SUM(EP12:EP32)</f>
         <v/>
       </c>
@@ -14658,7 +14772,7 @@
     <row r="35" ht="21" customFormat="1" customHeight="1" s="15">
       <c r="A35" s="14" t="n"/>
       <c r="B35" s="19" t="n"/>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="C35" s="88" t="inlineStr">
         <is>
           <t>EQUIPMENT</t>
         </is>
@@ -17589,7 +17703,7 @@
     <row r="53" ht="72" customFormat="1" customHeight="1" s="15">
       <c r="A53" s="14" t="n"/>
       <c r="B53" s="19" t="n"/>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C53" s="89" t="inlineStr">
         <is>
           <t>Description of work accomplished, issues encountered, etc.</t>
         </is>
@@ -17612,220 +17726,220 @@
           <t xml:space="preserve">Job Specific </t>
         </is>
       </c>
-      <c r="R53" s="78" t="n"/>
-      <c r="S53" s="78" t="n"/>
-      <c r="T53" s="78" t="n"/>
-      <c r="U53" s="79" t="n"/>
+      <c r="R53" s="90" t="n"/>
+      <c r="S53" s="90" t="n"/>
+      <c r="T53" s="90" t="n"/>
+      <c r="U53" s="91" t="n"/>
       <c r="V53" s="61" t="n"/>
       <c r="W53" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">Job Specific </t>
         </is>
       </c>
-      <c r="X53" s="78" t="n"/>
-      <c r="Y53" s="78" t="n"/>
-      <c r="Z53" s="78" t="n"/>
-      <c r="AA53" s="79" t="n"/>
+      <c r="X53" s="90" t="n"/>
+      <c r="Y53" s="90" t="n"/>
+      <c r="Z53" s="90" t="n"/>
+      <c r="AA53" s="91" t="n"/>
       <c r="AB53" s="61" t="n"/>
       <c r="AC53" s="76" t="inlineStr">
         <is>
           <t xml:space="preserve">Job Specific </t>
         </is>
       </c>
-      <c r="AD53" s="78" t="n"/>
-      <c r="AE53" s="78" t="n"/>
-      <c r="AF53" s="78" t="n"/>
-      <c r="AG53" s="79" t="n"/>
+      <c r="AD53" s="90" t="n"/>
+      <c r="AE53" s="90" t="n"/>
+      <c r="AF53" s="90" t="n"/>
+      <c r="AG53" s="91" t="n"/>
       <c r="AH53" s="61" t="n"/>
       <c r="AI53" s="76" t="inlineStr">
         <is>
           <t>Job Specific</t>
         </is>
       </c>
-      <c r="AJ53" s="78" t="n"/>
-      <c r="AK53" s="78" t="n"/>
-      <c r="AL53" s="78" t="n"/>
-      <c r="AM53" s="79" t="n"/>
+      <c r="AJ53" s="90" t="n"/>
+      <c r="AK53" s="90" t="n"/>
+      <c r="AL53" s="90" t="n"/>
+      <c r="AM53" s="91" t="n"/>
       <c r="AN53" s="61" t="n"/>
       <c r="AO53" s="76" t="inlineStr">
         <is>
           <t>Job Specific</t>
         </is>
       </c>
-      <c r="AP53" s="78" t="n"/>
-      <c r="AQ53" s="78" t="n"/>
-      <c r="AR53" s="78" t="n"/>
-      <c r="AS53" s="79" t="n"/>
+      <c r="AP53" s="90" t="n"/>
+      <c r="AQ53" s="90" t="n"/>
+      <c r="AR53" s="90" t="n"/>
+      <c r="AS53" s="91" t="n"/>
       <c r="AT53" s="61" t="n"/>
       <c r="AU53" s="76" t="inlineStr">
         <is>
           <t>Job Specific</t>
         </is>
       </c>
-      <c r="AV53" s="78" t="n"/>
-      <c r="AW53" s="78" t="n"/>
-      <c r="AX53" s="78" t="n"/>
-      <c r="AY53" s="79" t="n"/>
+      <c r="AV53" s="90" t="n"/>
+      <c r="AW53" s="90" t="n"/>
+      <c r="AX53" s="90" t="n"/>
+      <c r="AY53" s="91" t="n"/>
       <c r="AZ53" s="61" t="n"/>
       <c r="BA53" s="76" t="inlineStr">
         <is>
           <t>Job Specific</t>
         </is>
       </c>
-      <c r="BB53" s="78" t="n"/>
-      <c r="BC53" s="78" t="n"/>
-      <c r="BD53" s="78" t="n"/>
-      <c r="BE53" s="79" t="n"/>
+      <c r="BB53" s="90" t="n"/>
+      <c r="BC53" s="90" t="n"/>
+      <c r="BD53" s="90" t="n"/>
+      <c r="BE53" s="91" t="n"/>
       <c r="BF53" s="61" t="n"/>
       <c r="BG53" s="76" t="inlineStr">
         <is>
           <t>Job Specific</t>
         </is>
       </c>
-      <c r="BH53" s="78" t="n"/>
-      <c r="BI53" s="78" t="n"/>
-      <c r="BJ53" s="78" t="n"/>
-      <c r="BK53" s="79" t="n"/>
+      <c r="BH53" s="90" t="n"/>
+      <c r="BI53" s="90" t="n"/>
+      <c r="BJ53" s="90" t="n"/>
+      <c r="BK53" s="91" t="n"/>
       <c r="BL53" s="61" t="n"/>
       <c r="BM53" s="76" t="inlineStr">
         <is>
           <t>Job Specific</t>
         </is>
       </c>
-      <c r="BN53" s="78" t="n"/>
-      <c r="BO53" s="78" t="n"/>
-      <c r="BP53" s="78" t="n"/>
-      <c r="BQ53" s="79" t="n"/>
+      <c r="BN53" s="90" t="n"/>
+      <c r="BO53" s="90" t="n"/>
+      <c r="BP53" s="90" t="n"/>
+      <c r="BQ53" s="91" t="n"/>
       <c r="BR53" s="61" t="n"/>
       <c r="BS53" s="76" t="inlineStr">
         <is>
           <t>Job Specific</t>
         </is>
       </c>
-      <c r="BT53" s="78" t="n"/>
-      <c r="BU53" s="78" t="n"/>
-      <c r="BV53" s="78" t="n"/>
-      <c r="BW53" s="79" t="n"/>
+      <c r="BT53" s="90" t="n"/>
+      <c r="BU53" s="90" t="n"/>
+      <c r="BV53" s="90" t="n"/>
+      <c r="BW53" s="91" t="n"/>
       <c r="BX53" s="61" t="n"/>
       <c r="BY53" s="76" t="inlineStr">
         <is>
           <t>Job Specific</t>
         </is>
       </c>
-      <c r="BZ53" s="78" t="n"/>
-      <c r="CA53" s="78" t="n"/>
-      <c r="CB53" s="78" t="n"/>
-      <c r="CC53" s="79" t="n"/>
+      <c r="BZ53" s="90" t="n"/>
+      <c r="CA53" s="90" t="n"/>
+      <c r="CB53" s="90" t="n"/>
+      <c r="CC53" s="91" t="n"/>
       <c r="CD53" s="61" t="n"/>
       <c r="CE53" s="76" t="inlineStr">
         <is>
           <t>Job Specific</t>
         </is>
       </c>
-      <c r="CF53" s="78" t="n"/>
-      <c r="CG53" s="78" t="n"/>
-      <c r="CH53" s="78" t="n"/>
-      <c r="CI53" s="79" t="n"/>
+      <c r="CF53" s="90" t="n"/>
+      <c r="CG53" s="90" t="n"/>
+      <c r="CH53" s="90" t="n"/>
+      <c r="CI53" s="91" t="n"/>
       <c r="CJ53" s="61" t="n"/>
       <c r="CK53" s="76" t="inlineStr">
         <is>
           <t>Job Specific</t>
         </is>
       </c>
-      <c r="CL53" s="78" t="n"/>
-      <c r="CM53" s="78" t="n"/>
-      <c r="CN53" s="78" t="n"/>
-      <c r="CO53" s="79" t="n"/>
+      <c r="CL53" s="90" t="n"/>
+      <c r="CM53" s="90" t="n"/>
+      <c r="CN53" s="90" t="n"/>
+      <c r="CO53" s="91" t="n"/>
       <c r="CP53" s="61" t="n"/>
       <c r="CQ53" s="76" t="inlineStr">
         <is>
           <t>Job Specific</t>
         </is>
       </c>
-      <c r="CR53" s="78" t="n"/>
-      <c r="CS53" s="78" t="n"/>
-      <c r="CT53" s="78" t="n"/>
-      <c r="CU53" s="79" t="n"/>
+      <c r="CR53" s="90" t="n"/>
+      <c r="CS53" s="90" t="n"/>
+      <c r="CT53" s="90" t="n"/>
+      <c r="CU53" s="91" t="n"/>
       <c r="CV53" s="61" t="n"/>
       <c r="CW53" s="76" t="inlineStr">
         <is>
           <t>Job Specific</t>
         </is>
       </c>
-      <c r="CX53" s="78" t="n"/>
-      <c r="CY53" s="78" t="n"/>
-      <c r="CZ53" s="78" t="n"/>
-      <c r="DA53" s="79" t="n"/>
+      <c r="CX53" s="90" t="n"/>
+      <c r="CY53" s="90" t="n"/>
+      <c r="CZ53" s="90" t="n"/>
+      <c r="DA53" s="91" t="n"/>
       <c r="DB53" s="61" t="n"/>
       <c r="DC53" s="76" t="inlineStr">
         <is>
           <t>Job Specific</t>
         </is>
       </c>
-      <c r="DD53" s="78" t="n"/>
-      <c r="DE53" s="78" t="n"/>
-      <c r="DF53" s="78" t="n"/>
-      <c r="DG53" s="79" t="n"/>
+      <c r="DD53" s="90" t="n"/>
+      <c r="DE53" s="90" t="n"/>
+      <c r="DF53" s="90" t="n"/>
+      <c r="DG53" s="91" t="n"/>
       <c r="DH53" s="61" t="n"/>
       <c r="DI53" s="76" t="inlineStr">
         <is>
           <t>Job Specific</t>
         </is>
       </c>
-      <c r="DJ53" s="78" t="n"/>
-      <c r="DK53" s="78" t="n"/>
-      <c r="DL53" s="78" t="n"/>
-      <c r="DM53" s="79" t="n"/>
+      <c r="DJ53" s="90" t="n"/>
+      <c r="DK53" s="90" t="n"/>
+      <c r="DL53" s="90" t="n"/>
+      <c r="DM53" s="91" t="n"/>
       <c r="DN53" s="61" t="n"/>
       <c r="DO53" s="76" t="inlineStr">
         <is>
           <t>Job Specific</t>
         </is>
       </c>
-      <c r="DP53" s="78" t="n"/>
-      <c r="DQ53" s="78" t="n"/>
-      <c r="DR53" s="78" t="n"/>
-      <c r="DS53" s="79" t="n"/>
+      <c r="DP53" s="90" t="n"/>
+      <c r="DQ53" s="90" t="n"/>
+      <c r="DR53" s="90" t="n"/>
+      <c r="DS53" s="91" t="n"/>
       <c r="DT53" s="61" t="n"/>
       <c r="DU53" s="76" t="inlineStr">
         <is>
           <t>Job Specific</t>
         </is>
       </c>
-      <c r="DV53" s="78" t="n"/>
-      <c r="DW53" s="78" t="n"/>
-      <c r="DX53" s="78" t="n"/>
-      <c r="DY53" s="79" t="n"/>
+      <c r="DV53" s="90" t="n"/>
+      <c r="DW53" s="90" t="n"/>
+      <c r="DX53" s="90" t="n"/>
+      <c r="DY53" s="91" t="n"/>
       <c r="DZ53" s="61" t="n"/>
       <c r="EA53" s="76" t="inlineStr">
         <is>
           <t>Job Specific</t>
         </is>
       </c>
-      <c r="EB53" s="78" t="n"/>
-      <c r="EC53" s="78" t="n"/>
-      <c r="ED53" s="78" t="n"/>
-      <c r="EE53" s="79" t="n"/>
+      <c r="EB53" s="90" t="n"/>
+      <c r="EC53" s="90" t="n"/>
+      <c r="ED53" s="90" t="n"/>
+      <c r="EE53" s="91" t="n"/>
       <c r="EF53" s="61" t="n"/>
       <c r="EG53" s="76" t="inlineStr">
         <is>
           <t>Job Specific</t>
         </is>
       </c>
-      <c r="EH53" s="78" t="n"/>
-      <c r="EI53" s="78" t="n"/>
-      <c r="EJ53" s="78" t="n"/>
-      <c r="EK53" s="79" t="n"/>
+      <c r="EH53" s="90" t="n"/>
+      <c r="EI53" s="90" t="n"/>
+      <c r="EJ53" s="90" t="n"/>
+      <c r="EK53" s="91" t="n"/>
       <c r="EL53" s="61" t="n"/>
       <c r="EM53" s="76" t="inlineStr">
         <is>
           <t>Job Specific</t>
         </is>
       </c>
-      <c r="EN53" s="78" t="n"/>
-      <c r="EO53" s="78" t="n"/>
-      <c r="EP53" s="78" t="n"/>
-      <c r="EQ53" s="79" t="n"/>
+      <c r="EN53" s="90" t="n"/>
+      <c r="EO53" s="90" t="n"/>
+      <c r="EP53" s="90" t="n"/>
+      <c r="EQ53" s="91" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="22">
